--- a/Data/Temp/InvoicesReport UI Extraction.xlsx
+++ b/Data/Temp/InvoicesReport UI Extraction.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanielRicardoRochaQu\Downloads\Invoicing Bot\Recon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1184" documentId="13_ncr:1_{B5D6CEAF-E681-4588-8E6E-EF4492DB7BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{358C4E9F-51B2-44E2-A3DF-B8066D6F11A4}"/>
+  <xr:revisionPtr revIDLastSave="1196" documentId="13_ncr:1_{B5D6CEAF-E681-4588-8E6E-EF4492DB7BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE0624E3-C2BC-4C2B-B914-8771901DB73F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="6" xr2:uid="{70E8A791-13CE-4BD4-B2C5-703777F4F9B6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="6" xr2:uid="{70E8A791-13CE-4BD4-B2C5-703777F4F9B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoices Report Input" sheetId="8" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="145">
   <si>
     <t>RECORD ID - INVOICES</t>
   </si>
@@ -494,6 +494,15 @@
   </si>
   <si>
     <t>Reseller International</t>
+  </si>
+  <si>
+    <t>Client Staff Bonus</t>
+  </si>
+  <si>
+    <t>GST Free Income</t>
+  </si>
+  <si>
+    <t>Exempt Income</t>
   </si>
 </sst>
 </file>
@@ -1395,8 +1404,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}" name="Xero_Tax_Acc" displayName="Xero_Tax_Acc" ref="A1:F181" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:F181" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}" name="Xero_Tax_Acc" displayName="Xero_Tax_Acc" ref="A1:F183" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:F183" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{ADF06759-72AB-4C84-B20B-0E8D66CF7A70}" name="Line Item"/>
     <tableColumn id="4" xr3:uid="{136FB1F1-5689-4097-ACD2-3191F8E3FAEA}" name="Currency"/>
@@ -3403,7 +3412,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06CC148B-0B9B-443B-9640-E0693778E85E}">
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
@@ -3456,7 +3465,7 @@
         <v>FT Accountant - AUD - Sales Pipeline</v>
       </c>
       <c r="H2" t="str" cm="1">
-        <f t="array" ref="H2:H180">+_xlfn.UNIQUE(Xero_Tax_Acc[LineItem_Key])</f>
+        <f t="array" ref="H2:H182">+_xlfn.UNIQUE(Xero_Tax_Acc[LineItem_Key])</f>
         <v>FT Accountant - AUD - Sales Pipeline</v>
       </c>
     </row>
@@ -6980,7 +6989,7 @@
       <c r="E149">
         <v>406</v>
       </c>
-      <c r="F149" s="11" t="str">
+      <c r="F149" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - Dripify License - AUD - Franchise Pipeline</v>
       </c>
@@ -7004,7 +7013,7 @@
       <c r="E150">
         <v>406</v>
       </c>
-      <c r="F150" s="11" t="str">
+      <c r="F150" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>1Password License - AUD - Franchise Pipeline</v>
       </c>
@@ -7028,7 +7037,7 @@
       <c r="E151">
         <v>406</v>
       </c>
-      <c r="F151" s="11" t="str">
+      <c r="F151" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS Email Only + 1Password - AUD - Franchise Pipeline</v>
       </c>
@@ -7052,7 +7061,7 @@
       <c r="E152">
         <v>406</v>
       </c>
-      <c r="F152" s="11" t="str">
+      <c r="F152" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - HubSpot Sales License - AUD - Franchise Pipeline</v>
       </c>
@@ -7076,7 +7085,7 @@
       <c r="E153">
         <v>406</v>
       </c>
-      <c r="F153" s="11" t="str">
+      <c r="F153" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS CoPilot License - AUD - Franchise Pipeline</v>
       </c>
@@ -7100,7 +7109,7 @@
       <c r="E154">
         <v>406</v>
       </c>
-      <c r="F154" s="11" t="str">
+      <c r="F154" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>HubSpot Sales License - AUD - Franchise Pipeline</v>
       </c>
@@ -7124,7 +7133,7 @@
       <c r="E155">
         <v>406</v>
       </c>
-      <c r="F155" s="11" t="str">
+      <c r="F155" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - Apollo License - AUD - Franchise Pipeline</v>
       </c>
@@ -7148,7 +7157,7 @@
       <c r="E156">
         <v>406</v>
       </c>
-      <c r="F156" s="11" t="str">
+      <c r="F156" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS Email Only - AUD - Franchise Pipeline</v>
       </c>
@@ -7172,7 +7181,7 @@
       <c r="E157">
         <v>406</v>
       </c>
-      <c r="F157" s="11" t="str">
+      <c r="F157" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS O365 License + 1Password - AUD - Franchise Pipeline</v>
       </c>
@@ -7196,7 +7205,7 @@
       <c r="E158">
         <v>406</v>
       </c>
-      <c r="F158" s="11" t="str">
+      <c r="F158" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Dripify License - AUD - Franchise Pipeline</v>
       </c>
@@ -7220,7 +7229,7 @@
       <c r="E159">
         <v>405</v>
       </c>
-      <c r="F159" s="11" t="str">
+      <c r="F159" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Annual Conference Fee - AUD - Franchise Pipeline</v>
       </c>
@@ -7244,7 +7253,7 @@
       <c r="E160">
         <v>406</v>
       </c>
-      <c r="F160" s="11" t="str">
+      <c r="F160" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MS CoPilot License - AUD - Franchise Pipeline</v>
       </c>
@@ -7268,7 +7277,7 @@
       <c r="E161">
         <v>406</v>
       </c>
-      <c r="F161" s="11" t="str">
+      <c r="F161" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MS O365 License + 1Password - AUD - Franchise Pipeline</v>
       </c>
@@ -7292,7 +7301,7 @@
       <c r="E162">
         <v>406</v>
       </c>
-      <c r="F162" s="11" t="str">
+      <c r="F162" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Apollo License - AUD - Franchise Pipeline</v>
       </c>
@@ -7316,7 +7325,7 @@
       <c r="E163">
         <v>4300</v>
       </c>
-      <c r="F163" s="11" t="str">
+      <c r="F163" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analyst - AUD - Sales Pipeline</v>
       </c>
@@ -7340,7 +7349,7 @@
       <c r="E164">
         <v>404</v>
       </c>
-      <c r="F164" s="11" t="str">
+      <c r="F164" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Reseller International - AUD - Reseller Pipeline</v>
       </c>
@@ -7364,7 +7373,7 @@
       <c r="E165">
         <v>404</v>
       </c>
-      <c r="F165" s="11" t="str">
+      <c r="F165" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Reseller Monthly Fee - AUD - Reseller Pipeline</v>
       </c>
@@ -7388,7 +7397,7 @@
       <c r="E166">
         <v>406</v>
       </c>
-      <c r="F166" s="11" t="str">
+      <c r="F166" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - Dripify License - GBP - Franchise Pipeline</v>
       </c>
@@ -7412,7 +7421,7 @@
       <c r="E167">
         <v>406</v>
       </c>
-      <c r="F167" s="11" t="str">
+      <c r="F167" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>1Password License - GBP - Franchise Pipeline</v>
       </c>
@@ -7436,7 +7445,7 @@
       <c r="E168">
         <v>406</v>
       </c>
-      <c r="F168" s="11" t="str">
+      <c r="F168" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS Email Only + 1Password - GBP - Franchise Pipeline</v>
       </c>
@@ -7460,7 +7469,7 @@
       <c r="E169">
         <v>406</v>
       </c>
-      <c r="F169" s="11" t="str">
+      <c r="F169" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - HubSpot Sales License - GBP - Franchise Pipeline</v>
       </c>
@@ -7484,7 +7493,7 @@
       <c r="E170">
         <v>406</v>
       </c>
-      <c r="F170" s="11" t="str">
+      <c r="F170" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS CoPilot License - GBP - Franchise Pipeline</v>
       </c>
@@ -7508,7 +7517,7 @@
       <c r="E171">
         <v>406</v>
       </c>
-      <c r="F171" s="11" t="str">
+      <c r="F171" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>HubSpot Sales License - GBP - Franchise Pipeline</v>
       </c>
@@ -7532,7 +7541,7 @@
       <c r="E172">
         <v>406</v>
       </c>
-      <c r="F172" s="11" t="str">
+      <c r="F172" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - Apollo License - GBP - Franchise Pipeline</v>
       </c>
@@ -7556,7 +7565,7 @@
       <c r="E173">
         <v>406</v>
       </c>
-      <c r="F173" s="11" t="str">
+      <c r="F173" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS Email Only - GBP - Franchise Pipeline</v>
       </c>
@@ -7580,7 +7589,7 @@
       <c r="E174">
         <v>406</v>
       </c>
-      <c r="F174" s="11" t="str">
+      <c r="F174" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS O365 License + 1Password - GBP - Franchise Pipeline</v>
       </c>
@@ -7604,7 +7613,7 @@
       <c r="E175">
         <v>406</v>
       </c>
-      <c r="F175" s="11" t="str">
+      <c r="F175" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Dripify License - GBP - Franchise Pipeline</v>
       </c>
@@ -7628,7 +7637,7 @@
       <c r="E176">
         <v>406</v>
       </c>
-      <c r="F176" s="11" t="str">
+      <c r="F176" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Annual Conference Fee - GBP - Franchise Pipeline</v>
       </c>
@@ -7652,7 +7661,7 @@
       <c r="E177">
         <v>406</v>
       </c>
-      <c r="F177" s="11" t="str">
+      <c r="F177" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MS CoPilot License - GBP - Franchise Pipeline</v>
       </c>
@@ -7676,7 +7685,7 @@
       <c r="E178">
         <v>406</v>
       </c>
-      <c r="F178" s="11" t="str">
+      <c r="F178" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MS O365 License + 1Password - GBP - Franchise Pipeline</v>
       </c>
@@ -7700,7 +7709,7 @@
       <c r="E179">
         <v>406</v>
       </c>
-      <c r="F179" s="11" t="str">
+      <c r="F179" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Apollo License - GBP - Franchise Pipeline</v>
       </c>
@@ -7724,7 +7733,7 @@
       <c r="E180">
         <v>4300</v>
       </c>
-      <c r="F180" s="11" t="str">
+      <c r="F180" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analyst - GBP - Sales Pipeline</v>
       </c>
@@ -7748,9 +7757,57 @@
       <c r="E181">
         <v>4400</v>
       </c>
-      <c r="F181" s="11" t="str">
+      <c r="F181" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Reseller International - GBP - Reseller Pipeline</v>
+      </c>
+      <c r="H181" t="str">
+        <v>Client Staff Bonus - AUD - Sales Pipeline</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" t="s">
+        <v>142</v>
+      </c>
+      <c r="B182" t="s">
+        <v>40</v>
+      </c>
+      <c r="C182" t="s">
+        <v>41</v>
+      </c>
+      <c r="D182" t="s">
+        <v>143</v>
+      </c>
+      <c r="E182">
+        <v>280</v>
+      </c>
+      <c r="F182" s="11" t="str">
+        <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
+        <v>Client Staff Bonus - AUD - Sales Pipeline</v>
+      </c>
+      <c r="H182" t="str">
+        <v>Client Staff Bonus - GBP - Sales Pipeline</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" t="s">
+        <v>142</v>
+      </c>
+      <c r="B183" t="s">
+        <v>51</v>
+      </c>
+      <c r="C183" t="s">
+        <v>41</v>
+      </c>
+      <c r="D183" t="s">
+        <v>144</v>
+      </c>
+      <c r="E183">
+        <v>260</v>
+      </c>
+      <c r="F183" s="11" t="str">
+        <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
+        <v>Client Staff Bonus - GBP - Sales Pipeline</v>
       </c>
     </row>
   </sheetData>
@@ -7762,14 +7819,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="2b4b3f37-1cd0-4b26-90f2-9948314503a5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca9c0abd-4151-432c-97d3-4a3f10bfee7f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8014,16 +8069,18 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="2b4b3f37-1cd0-4b26-90f2-9948314503a5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca9c0abd-4151-432c-97d3-4a3f10bfee7f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A88FCA88-4CCB-4A2A-8432-786A6791AF57}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60A3338-C622-4FF5-BFA9-54DFDA479994}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8031,5 +8088,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60A3338-C622-4FF5-BFA9-54DFDA479994}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A88FCA88-4CCB-4A2A-8432-786A6791AF57}"/>
 </file>
--- a/Data/Temp/InvoicesReport UI Extraction.xlsx
+++ b/Data/Temp/InvoicesReport UI Extraction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanielRicardoRochaQu\Downloads\Invoicing Bot\Recon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1196" documentId="13_ncr:1_{B5D6CEAF-E681-4588-8E6E-EF4492DB7BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE0624E3-C2BC-4C2B-B914-8771901DB73F}"/>
+  <xr:revisionPtr revIDLastSave="1197" documentId="13_ncr:1_{B5D6CEAF-E681-4588-8E6E-EF4492DB7BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56B9B8CA-9194-4DB4-B514-B4A64D88B0B5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="6" xr2:uid="{70E8A791-13CE-4BD4-B2C5-703777F4F9B6}"/>
   </bookViews>
@@ -1052,7 +1052,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1064,7 +1064,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1405,7 +1404,21 @@
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}" name="Xero_Tax_Acc" displayName="Xero_Tax_Acc" ref="A1:F183" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:F183" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}"/>
+  <autoFilter ref="A1:F183" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Annual Conference Fee"/>
+        <filter val="Background Verification Check Fee"/>
+        <filter val="Franchise Setup Fee"/>
+        <filter val="Monthly Advertisement Fee"/>
+        <filter val="Monthly Annual Conference Fee"/>
+        <filter val="Monthly Consultant Access Fee"/>
+        <filter val="Monthly Lead Gen Tech Stack Fee"/>
+        <filter val="Monthly Support Fee"/>
+        <filter val="Reseller Monthly Fee"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{ADF06759-72AB-4C84-B20B-0E8D66CF7A70}" name="Line Item"/>
     <tableColumn id="4" xr3:uid="{136FB1F1-5689-4097-ACD2-3191F8E3FAEA}" name="Currency"/>
@@ -3444,7 +3457,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" hidden="1">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -3469,7 +3482,7 @@
         <v>FT Accountant - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" hidden="1">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -3493,7 +3506,7 @@
         <v>FT Zoho Developer - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" hidden="1">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -3517,7 +3530,7 @@
         <v>PT Wealth Management Paraplanner - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" hidden="1">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -3541,7 +3554,7 @@
         <v>FT Salesforce Developer - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" hidden="1">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -3565,7 +3578,7 @@
         <v>FT Wealth Management Paraplanner - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" hidden="1">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -3589,7 +3602,7 @@
         <v>Full Stack Developer - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" hidden="1">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -3613,7 +3626,7 @@
         <v>Custom Service - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" hidden="1">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -3637,7 +3650,7 @@
         <v>PT Wealth Management Virtual Assistant - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" hidden="1">
       <c r="A10" t="s">
         <v>81</v>
       </c>
@@ -3661,7 +3674,7 @@
         <v>FT Bookkeeping - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" hidden="1">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -3685,7 +3698,7 @@
         <v>Oracle HCM Cloud Developer - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" hidden="1">
       <c r="A12" t="s">
         <v>83</v>
       </c>
@@ -3709,7 +3722,7 @@
         <v>PT Zoho Developer - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" hidden="1">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -3733,7 +3746,7 @@
         <v>Full Time Custom Staff Aug - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" hidden="1">
       <c r="A14" t="s">
         <v>85</v>
       </c>
@@ -3757,7 +3770,7 @@
         <v>Full Time Medical Staff - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" hidden="1">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -3781,7 +3794,7 @@
         <v>Part Time Custom Staff Aug - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" hidden="1">
       <c r="A16" t="s">
         <v>87</v>
       </c>
@@ -3805,7 +3818,7 @@
         <v>PT Accountant - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" hidden="1">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -3829,7 +3842,7 @@
         <v>FT Wealth Management Virtual Assistant - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" hidden="1">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -3853,7 +3866,7 @@
         <v>PT Bookkeeping - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" hidden="1">
       <c r="A19" t="s">
         <v>90</v>
       </c>
@@ -3877,7 +3890,7 @@
         <v>Dedicated 24x7x365 Digital Assistant - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" hidden="1">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -3901,7 +3914,7 @@
         <v>Data Analytics Managed Service - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" hidden="1">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -3925,7 +3938,7 @@
         <v>Data Analytics Implementation - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" hidden="1">
       <c r="A22" t="s">
         <v>93</v>
       </c>
@@ -3949,7 +3962,7 @@
         <v>FT RPA Developer - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" hidden="1">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -3973,7 +3986,7 @@
         <v>DA Implementation Team - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" hidden="1">
       <c r="A24" t="s">
         <v>95</v>
       </c>
@@ -3997,7 +4010,7 @@
         <v>AI Data Extraction per page - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" hidden="1">
       <c r="A25" t="s">
         <v>96</v>
       </c>
@@ -4021,7 +4034,7 @@
         <v>Fractional Digital Assistant - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" hidden="1">
       <c r="A26" t="s">
         <v>97</v>
       </c>
@@ -4069,7 +4082,7 @@
         <v>Background Verification Check Fee - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" hidden="1">
       <c r="A28" t="s">
         <v>99</v>
       </c>
@@ -4093,7 +4106,7 @@
         <v>Onboarding Setup - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" hidden="1">
       <c r="A29" t="s">
         <v>100</v>
       </c>
@@ -4117,7 +4130,7 @@
         <v>T&amp;M Staff Augmentation - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" hidden="1">
       <c r="A30" t="s">
         <v>101</v>
       </c>
@@ -4141,7 +4154,7 @@
         <v>Custom Data Analytics Consulting - T&amp;M - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" hidden="1">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -4165,7 +4178,7 @@
         <v>Data Analytics - Basic Maintenance - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" hidden="1">
       <c r="A32" t="s">
         <v>103</v>
       </c>
@@ -4189,7 +4202,7 @@
         <v>Data Analytics - Light Managed Service - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" hidden="1">
       <c r="A33" t="s">
         <v>104</v>
       </c>
@@ -4213,7 +4226,7 @@
         <v>Data Analytics - Managed Service - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" hidden="1">
       <c r="A34" t="s">
         <v>105</v>
       </c>
@@ -4405,7 +4418,7 @@
         <v>Monthly Consultant Access Fee - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" hidden="1">
       <c r="A42" t="s">
         <v>113</v>
       </c>
@@ -4429,7 +4442,7 @@
         <v>COMPLEX - Ai Powered Data Extraction - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" hidden="1">
       <c r="A43" t="s">
         <v>114</v>
       </c>
@@ -4453,7 +4466,7 @@
         <v>Ai Powered Data Extraction - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" hidden="1">
       <c r="A44" t="s">
         <v>115</v>
       </c>
@@ -4477,7 +4490,7 @@
         <v>Digital Assistant - upto 250k Executions - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" hidden="1">
       <c r="A45" t="s">
         <v>116</v>
       </c>
@@ -4501,7 +4514,7 @@
         <v>Digital Assistant - upto 100k Executions - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" hidden="1">
       <c r="A46" t="s">
         <v>117</v>
       </c>
@@ -4525,7 +4538,7 @@
         <v>Digital Assistant - upto 50k Executions - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" hidden="1">
       <c r="A47" t="s">
         <v>118</v>
       </c>
@@ -4549,7 +4562,7 @@
         <v>Digital Assistant - upto 10k Executions - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" hidden="1">
       <c r="A48" t="s">
         <v>119</v>
       </c>
@@ -4573,7 +4586,7 @@
         <v>MSP Reseller - AUD - MSP Pipeline</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" hidden="1">
       <c r="A49" t="s">
         <v>121</v>
       </c>
@@ -4597,7 +4610,7 @@
         <v>MSP Referral Partner - AUD - MSP Pipeline</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" hidden="1">
       <c r="A50" t="s">
         <v>122</v>
       </c>
@@ -4621,7 +4634,7 @@
         <v>MSP Service Delivery Partner - AUD - MSP Pipeline</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" hidden="1">
       <c r="A51" t="s">
         <v>72</v>
       </c>
@@ -4645,7 +4658,7 @@
         <v>FT Accountant - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" hidden="1">
       <c r="A52" t="s">
         <v>74</v>
       </c>
@@ -4669,7 +4682,7 @@
         <v>FT Zoho Developer - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" hidden="1">
       <c r="A53" t="s">
         <v>75</v>
       </c>
@@ -4693,7 +4706,7 @@
         <v>PT Wealth Management Paraplanner - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" hidden="1">
       <c r="A54" t="s">
         <v>76</v>
       </c>
@@ -4717,7 +4730,7 @@
         <v>FT Salesforce Developer - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" hidden="1">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -4741,7 +4754,7 @@
         <v>FT Wealth Management Paraplanner - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" hidden="1">
       <c r="A56" t="s">
         <v>78</v>
       </c>
@@ -4765,7 +4778,7 @@
         <v>Full Stack Developer - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" hidden="1">
       <c r="A57" t="s">
         <v>79</v>
       </c>
@@ -4789,7 +4802,7 @@
         <v>Custom Service - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" hidden="1">
       <c r="A58" t="s">
         <v>80</v>
       </c>
@@ -4813,7 +4826,7 @@
         <v>PT Wealth Management Virtual Assistant - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" hidden="1">
       <c r="A59" t="s">
         <v>81</v>
       </c>
@@ -4837,7 +4850,7 @@
         <v>FT Bookkeeping - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" hidden="1">
       <c r="A60" t="s">
         <v>82</v>
       </c>
@@ -4861,7 +4874,7 @@
         <v>Oracle HCM Cloud Developer - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" hidden="1">
       <c r="A61" t="s">
         <v>83</v>
       </c>
@@ -4885,7 +4898,7 @@
         <v>PT Zoho Developer - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" hidden="1">
       <c r="A62" t="s">
         <v>84</v>
       </c>
@@ -4909,7 +4922,7 @@
         <v>Full Time Custom Staff Aug - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" hidden="1">
       <c r="A63" t="s">
         <v>85</v>
       </c>
@@ -4933,7 +4946,7 @@
         <v>Full Time Medical Staff - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" hidden="1">
       <c r="A64" t="s">
         <v>86</v>
       </c>
@@ -4957,7 +4970,7 @@
         <v>Part Time Custom Staff Aug - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" hidden="1">
       <c r="A65" t="s">
         <v>87</v>
       </c>
@@ -4981,7 +4994,7 @@
         <v>PT Accountant - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" hidden="1">
       <c r="A66" t="s">
         <v>88</v>
       </c>
@@ -5005,7 +5018,7 @@
         <v>FT Wealth Management Virtual Assistant - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" hidden="1">
       <c r="A67" t="s">
         <v>89</v>
       </c>
@@ -5029,7 +5042,7 @@
         <v>PT Bookkeeping - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" hidden="1">
       <c r="A68" t="s">
         <v>90</v>
       </c>
@@ -5053,7 +5066,7 @@
         <v>Dedicated 24x7x365 Digital Assistant - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" hidden="1">
       <c r="A69" t="s">
         <v>91</v>
       </c>
@@ -5077,7 +5090,7 @@
         <v>Data Analytics Managed Service - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" hidden="1">
       <c r="A70" t="s">
         <v>92</v>
       </c>
@@ -5101,7 +5114,7 @@
         <v>Data Analytics Implementation - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" hidden="1">
       <c r="A71" t="s">
         <v>93</v>
       </c>
@@ -5125,7 +5138,7 @@
         <v>FT RPA Developer - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" hidden="1">
       <c r="A72" t="s">
         <v>94</v>
       </c>
@@ -5149,7 +5162,7 @@
         <v>DA Implementation Team - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" hidden="1">
       <c r="A73" t="s">
         <v>95</v>
       </c>
@@ -5173,7 +5186,7 @@
         <v>AI Data Extraction per page - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" hidden="1">
       <c r="A74" t="s">
         <v>96</v>
       </c>
@@ -5197,7 +5210,7 @@
         <v>Fractional Digital Assistant - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" hidden="1">
       <c r="A75" t="s">
         <v>97</v>
       </c>
@@ -5245,7 +5258,7 @@
         <v>Background Verification Check Fee - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" hidden="1">
       <c r="A77" t="s">
         <v>99</v>
       </c>
@@ -5269,7 +5282,7 @@
         <v>Onboarding Setup - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" hidden="1">
       <c r="A78" t="s">
         <v>100</v>
       </c>
@@ -5293,7 +5306,7 @@
         <v>T&amp;M Staff Augmentation - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" hidden="1">
       <c r="A79" t="s">
         <v>101</v>
       </c>
@@ -5317,7 +5330,7 @@
         <v>Custom Data Analytics Consulting - T&amp;M - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" hidden="1">
       <c r="A80" t="s">
         <v>102</v>
       </c>
@@ -5341,7 +5354,7 @@
         <v>Data Analytics - Basic Maintenance - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" hidden="1">
       <c r="A81" t="s">
         <v>103</v>
       </c>
@@ -5365,7 +5378,7 @@
         <v>Data Analytics - Light Managed Service - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" hidden="1">
       <c r="A82" t="s">
         <v>104</v>
       </c>
@@ -5389,7 +5402,7 @@
         <v>Data Analytics - Managed Service - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" hidden="1">
       <c r="A83" t="s">
         <v>105</v>
       </c>
@@ -5581,7 +5594,7 @@
         <v>Monthly Consultant Access Fee - NZD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" hidden="1">
       <c r="A91" t="s">
         <v>113</v>
       </c>
@@ -5605,7 +5618,7 @@
         <v>COMPLEX - Ai Powered Data Extraction - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" hidden="1">
       <c r="A92" t="s">
         <v>114</v>
       </c>
@@ -5629,7 +5642,7 @@
         <v>Ai Powered Data Extraction - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" hidden="1">
       <c r="A93" t="s">
         <v>115</v>
       </c>
@@ -5653,7 +5666,7 @@
         <v>Digital Assistant - upto 250k Executions - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" hidden="1">
       <c r="A94" t="s">
         <v>116</v>
       </c>
@@ -5677,7 +5690,7 @@
         <v>Digital Assistant - upto 100k Executions - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" hidden="1">
       <c r="A95" t="s">
         <v>117</v>
       </c>
@@ -5701,7 +5714,7 @@
         <v>Digital Assistant - upto 50k Executions - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" hidden="1">
       <c r="A96" t="s">
         <v>118</v>
       </c>
@@ -5725,7 +5738,7 @@
         <v>Digital Assistant - upto 10k Executions - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" hidden="1">
       <c r="A97" t="s">
         <v>119</v>
       </c>
@@ -5749,7 +5762,7 @@
         <v>MSP Reseller - NZD - MSP Pipeline</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" hidden="1">
       <c r="A98" t="s">
         <v>121</v>
       </c>
@@ -5773,7 +5786,7 @@
         <v>MSP Referral Partner - NZD - MSP Pipeline</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" hidden="1">
       <c r="A99" t="s">
         <v>122</v>
       </c>
@@ -5797,7 +5810,7 @@
         <v>MSP Service Delivery Partner - NZD - MSP Pipeline</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" hidden="1">
       <c r="A100" t="s">
         <v>72</v>
       </c>
@@ -5821,7 +5834,7 @@
         <v>FT Accountant - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" hidden="1">
       <c r="A101" t="s">
         <v>74</v>
       </c>
@@ -5845,7 +5858,7 @@
         <v>FT Zoho Developer - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" hidden="1">
       <c r="A102" t="s">
         <v>75</v>
       </c>
@@ -5869,7 +5882,7 @@
         <v>PT Wealth Management Paraplanner - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" hidden="1">
       <c r="A103" t="s">
         <v>76</v>
       </c>
@@ -5893,7 +5906,7 @@
         <v>FT Salesforce Developer - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" hidden="1">
       <c r="A104" t="s">
         <v>77</v>
       </c>
@@ -5917,7 +5930,7 @@
         <v>FT Wealth Management Paraplanner - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" hidden="1">
       <c r="A105" t="s">
         <v>78</v>
       </c>
@@ -5941,7 +5954,7 @@
         <v>Full Stack Developer - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" hidden="1">
       <c r="A106" t="s">
         <v>79</v>
       </c>
@@ -5965,7 +5978,7 @@
         <v>Custom Service - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" hidden="1">
       <c r="A107" t="s">
         <v>80</v>
       </c>
@@ -5989,7 +6002,7 @@
         <v>PT Wealth Management Virtual Assistant - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" hidden="1">
       <c r="A108" t="s">
         <v>81</v>
       </c>
@@ -6013,7 +6026,7 @@
         <v>FT Bookkeeping - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" hidden="1">
       <c r="A109" t="s">
         <v>82</v>
       </c>
@@ -6037,7 +6050,7 @@
         <v>Oracle HCM Cloud Developer - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" hidden="1">
       <c r="A110" t="s">
         <v>83</v>
       </c>
@@ -6061,7 +6074,7 @@
         <v>PT Zoho Developer - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" hidden="1">
       <c r="A111" t="s">
         <v>84</v>
       </c>
@@ -6085,7 +6098,7 @@
         <v>Full Time Custom Staff Aug - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" hidden="1">
       <c r="A112" t="s">
         <v>85</v>
       </c>
@@ -6109,7 +6122,7 @@
         <v>Full Time Medical Staff - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" hidden="1">
       <c r="A113" t="s">
         <v>86</v>
       </c>
@@ -6133,7 +6146,7 @@
         <v>Part Time Custom Staff Aug - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" hidden="1">
       <c r="A114" t="s">
         <v>87</v>
       </c>
@@ -6157,7 +6170,7 @@
         <v>PT Accountant - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" hidden="1">
       <c r="A115" t="s">
         <v>88</v>
       </c>
@@ -6181,7 +6194,7 @@
         <v>FT Wealth Management Virtual Assistant - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" hidden="1">
       <c r="A116" t="s">
         <v>89</v>
       </c>
@@ -6205,7 +6218,7 @@
         <v>PT Bookkeeping - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" hidden="1">
       <c r="A117" t="s">
         <v>90</v>
       </c>
@@ -6229,7 +6242,7 @@
         <v>Dedicated 24x7x365 Digital Assistant - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" hidden="1">
       <c r="A118" t="s">
         <v>91</v>
       </c>
@@ -6253,7 +6266,7 @@
         <v>Data Analytics Managed Service - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" hidden="1">
       <c r="A119" t="s">
         <v>92</v>
       </c>
@@ -6277,7 +6290,7 @@
         <v>Data Analytics Implementation - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" hidden="1">
       <c r="A120" t="s">
         <v>93</v>
       </c>
@@ -6301,7 +6314,7 @@
         <v>FT RPA Developer - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" hidden="1">
       <c r="A121" t="s">
         <v>94</v>
       </c>
@@ -6325,7 +6338,7 @@
         <v>DA Implementation Team - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" hidden="1">
       <c r="A122" t="s">
         <v>95</v>
       </c>
@@ -6349,7 +6362,7 @@
         <v>AI Data Extraction per page - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" hidden="1">
       <c r="A123" t="s">
         <v>96</v>
       </c>
@@ -6373,7 +6386,7 @@
         <v>Fractional Digital Assistant - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" hidden="1">
       <c r="A124" t="s">
         <v>97</v>
       </c>
@@ -6421,7 +6434,7 @@
         <v>Background Verification Check Fee - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" hidden="1">
       <c r="A126" t="s">
         <v>99</v>
       </c>
@@ -6445,7 +6458,7 @@
         <v>Onboarding Setup - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" hidden="1">
       <c r="A127" t="s">
         <v>100</v>
       </c>
@@ -6469,7 +6482,7 @@
         <v>T&amp;M Staff Augmentation - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" hidden="1">
       <c r="A128" t="s">
         <v>101</v>
       </c>
@@ -6493,7 +6506,7 @@
         <v>Custom Data Analytics Consulting - T&amp;M - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" hidden="1">
       <c r="A129" t="s">
         <v>102</v>
       </c>
@@ -6517,7 +6530,7 @@
         <v>Data Analytics - Basic Maintenance - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" hidden="1">
       <c r="A130" t="s">
         <v>103</v>
       </c>
@@ -6541,7 +6554,7 @@
         <v>Data Analytics - Light Managed Service - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" hidden="1">
       <c r="A131" t="s">
         <v>104</v>
       </c>
@@ -6565,7 +6578,7 @@
         <v>Data Analytics - Managed Service - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" hidden="1">
       <c r="A132" t="s">
         <v>105</v>
       </c>
@@ -6757,7 +6770,7 @@
         <v>Monthly Consultant Access Fee - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" hidden="1">
       <c r="A140" t="s">
         <v>113</v>
       </c>
@@ -6781,7 +6794,7 @@
         <v>COMPLEX - Ai Powered Data Extraction - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" hidden="1">
       <c r="A141" t="s">
         <v>114</v>
       </c>
@@ -6805,7 +6818,7 @@
         <v>Ai Powered Data Extraction - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" hidden="1">
       <c r="A142" t="s">
         <v>115</v>
       </c>
@@ -6829,7 +6842,7 @@
         <v>Digital Assistant - upto 250k Executions - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" hidden="1">
       <c r="A143" t="s">
         <v>116</v>
       </c>
@@ -6853,7 +6866,7 @@
         <v>Digital Assistant - upto 100k Executions - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" hidden="1">
       <c r="A144" t="s">
         <v>117</v>
       </c>
@@ -6877,7 +6890,7 @@
         <v>Digital Assistant - upto 50k Executions - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" hidden="1">
       <c r="A145" t="s">
         <v>118</v>
       </c>
@@ -6901,7 +6914,7 @@
         <v>Digital Assistant - upto 10k Executions - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" hidden="1">
       <c r="A146" t="s">
         <v>119</v>
       </c>
@@ -6925,7 +6938,7 @@
         <v>MSP Reseller - GBP - MSP Pipeline</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" hidden="1">
       <c r="A147" t="s">
         <v>121</v>
       </c>
@@ -6949,7 +6962,7 @@
         <v>MSP Referral Partner - GBP - MSP Pipeline</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" hidden="1">
       <c r="A148" t="s">
         <v>122</v>
       </c>
@@ -6973,7 +6986,7 @@
         <v>MSP Service Delivery Partner - GBP - MSP Pipeline</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" hidden="1">
       <c r="A149" t="s">
         <v>126</v>
       </c>
@@ -6997,7 +7010,7 @@
         <v>Consultant - Dripify License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" hidden="1">
       <c r="A150" t="s">
         <v>127</v>
       </c>
@@ -7021,7 +7034,7 @@
         <v>1Password License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" hidden="1">
       <c r="A151" t="s">
         <v>128</v>
       </c>
@@ -7045,7 +7058,7 @@
         <v>Consultant - MS Email Only + 1Password - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" hidden="1">
       <c r="A152" t="s">
         <v>129</v>
       </c>
@@ -7069,7 +7082,7 @@
         <v>Consultant - HubSpot Sales License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" hidden="1">
       <c r="A153" t="s">
         <v>130</v>
       </c>
@@ -7093,7 +7106,7 @@
         <v>Consultant - MS CoPilot License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" hidden="1">
       <c r="A154" t="s">
         <v>131</v>
       </c>
@@ -7117,7 +7130,7 @@
         <v>HubSpot Sales License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" hidden="1">
       <c r="A155" t="s">
         <v>132</v>
       </c>
@@ -7141,7 +7154,7 @@
         <v>Consultant - Apollo License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" hidden="1">
       <c r="A156" t="s">
         <v>133</v>
       </c>
@@ -7165,7 +7178,7 @@
         <v>Consultant - MS Email Only - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" hidden="1">
       <c r="A157" t="s">
         <v>134</v>
       </c>
@@ -7189,7 +7202,7 @@
         <v>Consultant - MS O365 License + 1Password - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" hidden="1">
       <c r="A158" t="s">
         <v>135</v>
       </c>
@@ -7237,7 +7250,7 @@
         <v>Monthly Annual Conference Fee - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" hidden="1">
       <c r="A160" t="s">
         <v>137</v>
       </c>
@@ -7261,7 +7274,7 @@
         <v>MS CoPilot License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" hidden="1">
       <c r="A161" t="s">
         <v>138</v>
       </c>
@@ -7285,7 +7298,7 @@
         <v>MS O365 License + 1Password - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" hidden="1">
       <c r="A162" t="s">
         <v>139</v>
       </c>
@@ -7309,7 +7322,7 @@
         <v>Apollo License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" hidden="1">
       <c r="A163" t="s">
         <v>140</v>
       </c>
@@ -7333,7 +7346,7 @@
         <v>Data Analyst - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" hidden="1">
       <c r="A164" t="s">
         <v>141</v>
       </c>
@@ -7381,7 +7394,7 @@
         <v>Consultant - Dripify License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" hidden="1">
       <c r="A166" t="s">
         <v>126</v>
       </c>
@@ -7405,7 +7418,7 @@
         <v>1Password License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" hidden="1">
       <c r="A167" t="s">
         <v>127</v>
       </c>
@@ -7429,7 +7442,7 @@
         <v>Consultant - MS Email Only + 1Password - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" hidden="1">
       <c r="A168" t="s">
         <v>128</v>
       </c>
@@ -7453,7 +7466,7 @@
         <v>Consultant - HubSpot Sales License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" hidden="1">
       <c r="A169" t="s">
         <v>129</v>
       </c>
@@ -7477,7 +7490,7 @@
         <v>Consultant - MS CoPilot License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" hidden="1">
       <c r="A170" t="s">
         <v>130</v>
       </c>
@@ -7501,7 +7514,7 @@
         <v>HubSpot Sales License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" hidden="1">
       <c r="A171" t="s">
         <v>131</v>
       </c>
@@ -7525,7 +7538,7 @@
         <v>Consultant - Apollo License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" hidden="1">
       <c r="A172" t="s">
         <v>132</v>
       </c>
@@ -7549,7 +7562,7 @@
         <v>Consultant - MS Email Only - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" hidden="1">
       <c r="A173" t="s">
         <v>133</v>
       </c>
@@ -7573,7 +7586,7 @@
         <v>Consultant - MS O365 License + 1Password - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" hidden="1">
       <c r="A174" t="s">
         <v>134</v>
       </c>
@@ -7597,7 +7610,7 @@
         <v>Dripify License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" hidden="1">
       <c r="A175" t="s">
         <v>135</v>
       </c>
@@ -7645,7 +7658,7 @@
         <v>MS CoPilot License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" hidden="1">
       <c r="A177" t="s">
         <v>137</v>
       </c>
@@ -7669,7 +7682,7 @@
         <v>MS O365 License + 1Password - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" hidden="1">
       <c r="A178" t="s">
         <v>138</v>
       </c>
@@ -7693,7 +7706,7 @@
         <v>Apollo License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" hidden="1">
       <c r="A179" t="s">
         <v>139</v>
       </c>
@@ -7717,7 +7730,7 @@
         <v>Data Analyst - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" hidden="1">
       <c r="A180" t="s">
         <v>140</v>
       </c>
@@ -7741,7 +7754,7 @@
         <v>Reseller International - GBP - Reseller Pipeline</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" hidden="1">
       <c r="A181" t="s">
         <v>141</v>
       </c>
@@ -7765,7 +7778,7 @@
         <v>Client Staff Bonus - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" hidden="1">
       <c r="A182" t="s">
         <v>142</v>
       </c>
@@ -7781,7 +7794,7 @@
       <c r="E182">
         <v>280</v>
       </c>
-      <c r="F182" s="11" t="str">
+      <c r="F182" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Client Staff Bonus - AUD - Sales Pipeline</v>
       </c>
@@ -7789,7 +7802,7 @@
         <v>Client Staff Bonus - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" hidden="1">
       <c r="A183" t="s">
         <v>142</v>
       </c>
@@ -7805,7 +7818,7 @@
       <c r="E183">
         <v>260</v>
       </c>
-      <c r="F183" s="11" t="str">
+      <c r="F183" t="str">
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Client Staff Bonus - GBP - Sales Pipeline</v>
       </c>
@@ -7828,6 +7841,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="2b4b3f37-1cd0-4b26-90f2-9948314503a5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca9c0abd-4151-432c-97d3-4a3f10bfee7f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005F54BCC7603DAA4FB57C31851CA92685" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b666b694d6e76699e884a198b0fcc20b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ca9c0abd-4151-432c-97d3-4a3f10bfee7f" xmlns:ns3="2b4b3f37-1cd0-4b26-90f2-9948314503a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3e06c0a76cf39f93bdfa440a1b88f7bb" ns2:_="" ns3:_="">
     <xsd:import namespace="ca9c0abd-4151-432c-97d3-4a3f10bfee7f"/>
@@ -8068,25 +8092,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="2b4b3f37-1cd0-4b26-90f2-9948314503a5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca9c0abd-4151-432c-97d3-4a3f10bfee7f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60A3338-C622-4FF5-BFA9-54DFDA479994}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0554FEC5-F8C0-4A0B-9C72-9FC3334369E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A88FCA88-4CCB-4A2A-8432-786A6791AF57}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A88FCA88-4CCB-4A2A-8432-786A6791AF57}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0554FEC5-F8C0-4A0B-9C72-9FC3334369E2}"/>
 </file>
--- a/Data/Temp/InvoicesReport UI Extraction.xlsx
+++ b/Data/Temp/InvoicesReport UI Extraction.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanielRicardoRochaQu\Downloads\Invoicing Bot\Recon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1197" documentId="13_ncr:1_{B5D6CEAF-E681-4588-8E6E-EF4492DB7BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56B9B8CA-9194-4DB4-B514-B4A64D88B0B5}"/>
+  <xr:revisionPtr revIDLastSave="1207" documentId="13_ncr:1_{B5D6CEAF-E681-4588-8E6E-EF4492DB7BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3643793B-C3B7-4254-9E59-B5F912DC3CE2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="6" xr2:uid="{70E8A791-13CE-4BD4-B2C5-703777F4F9B6}"/>
   </bookViews>
@@ -1404,21 +1404,7 @@
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}" name="Xero_Tax_Acc" displayName="Xero_Tax_Acc" ref="A1:F183" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:F183" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Annual Conference Fee"/>
-        <filter val="Background Verification Check Fee"/>
-        <filter val="Franchise Setup Fee"/>
-        <filter val="Monthly Advertisement Fee"/>
-        <filter val="Monthly Annual Conference Fee"/>
-        <filter val="Monthly Consultant Access Fee"/>
-        <filter val="Monthly Lead Gen Tech Stack Fee"/>
-        <filter val="Monthly Support Fee"/>
-        <filter val="Reseller Monthly Fee"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F183" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{ADF06759-72AB-4C84-B20B-0E8D66CF7A70}" name="Line Item"/>
     <tableColumn id="4" xr3:uid="{136FB1F1-5689-4097-ACD2-3191F8E3FAEA}" name="Currency"/>
@@ -3425,7 +3411,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06CC148B-0B9B-443B-9640-E0693778E85E}">
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
@@ -3434,10 +3420,9 @@
     <col min="4" max="4" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="62.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="62.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -3457,7 +3442,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -3477,12 +3462,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Accountant - AUD - Sales Pipeline</v>
       </c>
-      <c r="H2" t="str" cm="1">
-        <f t="array" ref="H2:H182">+_xlfn.UNIQUE(Xero_Tax_Acc[LineItem_Key])</f>
-        <v>FT Accountant - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" hidden="1">
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -3502,11 +3483,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Zoho Developer - AUD - Sales Pipeline</v>
       </c>
-      <c r="H3" t="str">
-        <v>FT Zoho Developer - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" hidden="1">
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -3526,11 +3504,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Wealth Management Paraplanner - AUD - Sales Pipeline</v>
       </c>
-      <c r="H4" t="str">
-        <v>PT Wealth Management Paraplanner - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" hidden="1">
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -3550,11 +3525,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Salesforce Developer - AUD - Sales Pipeline</v>
       </c>
-      <c r="H5" t="str">
-        <v>FT Salesforce Developer - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" hidden="1">
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -3574,11 +3546,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Wealth Management Paraplanner - AUD - Sales Pipeline</v>
       </c>
-      <c r="H6" t="str">
-        <v>FT Wealth Management Paraplanner - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" hidden="1">
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -3598,11 +3567,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Full Stack Developer - AUD - Sales Pipeline</v>
       </c>
-      <c r="H7" t="str">
-        <v>Full Stack Developer - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" hidden="1">
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -3622,11 +3588,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Custom Service - AUD - Sales Pipeline</v>
       </c>
-      <c r="H8" t="str">
-        <v>Custom Service - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" hidden="1">
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -3646,11 +3609,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Wealth Management Virtual Assistant - AUD - Sales Pipeline</v>
       </c>
-      <c r="H9" t="str">
-        <v>PT Wealth Management Virtual Assistant - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1">
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>81</v>
       </c>
@@ -3670,11 +3630,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Bookkeeping - AUD - Sales Pipeline</v>
       </c>
-      <c r="H10" t="str">
-        <v>FT Bookkeeping - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" hidden="1">
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -3694,11 +3651,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Oracle HCM Cloud Developer - AUD - Sales Pipeline</v>
       </c>
-      <c r="H11" t="str">
-        <v>Oracle HCM Cloud Developer - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" hidden="1">
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>83</v>
       </c>
@@ -3718,11 +3672,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Zoho Developer - AUD - Sales Pipeline</v>
       </c>
-      <c r="H12" t="str">
-        <v>PT Zoho Developer - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1">
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -3742,11 +3693,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Full Time Custom Staff Aug - AUD - Sales Pipeline</v>
       </c>
-      <c r="H13" t="str">
-        <v>Full Time Custom Staff Aug - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" hidden="1">
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>85</v>
       </c>
@@ -3766,11 +3714,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Full Time Medical Staff - AUD - Sales Pipeline</v>
       </c>
-      <c r="H14" t="str">
-        <v>Full Time Medical Staff - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1">
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -3790,11 +3735,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Part Time Custom Staff Aug - AUD - Sales Pipeline</v>
       </c>
-      <c r="H15" t="str">
-        <v>Part Time Custom Staff Aug - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" hidden="1">
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>87</v>
       </c>
@@ -3814,11 +3756,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Accountant - AUD - Sales Pipeline</v>
       </c>
-      <c r="H16" t="str">
-        <v>PT Accountant - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" hidden="1">
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -3838,11 +3777,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Wealth Management Virtual Assistant - AUD - Sales Pipeline</v>
       </c>
-      <c r="H17" t="str">
-        <v>FT Wealth Management Virtual Assistant - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" hidden="1">
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -3862,11 +3798,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Bookkeeping - AUD - Sales Pipeline</v>
       </c>
-      <c r="H18" t="str">
-        <v>PT Bookkeeping - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" hidden="1">
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>90</v>
       </c>
@@ -3886,11 +3819,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Dedicated 24x7x365 Digital Assistant - AUD - Sales Pipeline</v>
       </c>
-      <c r="H19" t="str">
-        <v>Dedicated 24x7x365 Digital Assistant - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" hidden="1">
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -3910,11 +3840,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics Managed Service - AUD - Sales Pipeline</v>
       </c>
-      <c r="H20" t="str">
-        <v>Data Analytics Managed Service - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" hidden="1">
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -3934,11 +3861,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics Implementation - AUD - Sales Pipeline</v>
       </c>
-      <c r="H21" t="str">
-        <v>Data Analytics Implementation - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" hidden="1">
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>93</v>
       </c>
@@ -3958,11 +3882,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT RPA Developer - AUD - Sales Pipeline</v>
       </c>
-      <c r="H22" t="str">
-        <v>FT RPA Developer - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" hidden="1">
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -3982,11 +3903,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>DA Implementation Team - AUD - Sales Pipeline</v>
       </c>
-      <c r="H23" t="str">
-        <v>DA Implementation Team - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" hidden="1">
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>95</v>
       </c>
@@ -4006,11 +3924,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>AI Data Extraction per page - AUD - Sales Pipeline</v>
       </c>
-      <c r="H24" t="str">
-        <v>AI Data Extraction per page - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" hidden="1">
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>96</v>
       </c>
@@ -4030,11 +3945,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Fractional Digital Assistant - AUD - Sales Pipeline</v>
       </c>
-      <c r="H25" t="str">
-        <v>Fractional Digital Assistant - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" hidden="1">
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>97</v>
       </c>
@@ -4054,11 +3966,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>AI Workshop - AUD - Sales Pipeline</v>
       </c>
-      <c r="H26" t="str">
-        <v>AI Workshop - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -4078,11 +3987,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Background Verification Check Fee - AUD - Sales Pipeline</v>
       </c>
-      <c r="H27" t="str">
-        <v>Background Verification Check Fee - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" hidden="1">
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>99</v>
       </c>
@@ -4102,11 +4008,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Onboarding Setup - AUD - Sales Pipeline</v>
       </c>
-      <c r="H28" t="str">
-        <v>Onboarding Setup - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" hidden="1">
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>100</v>
       </c>
@@ -4126,11 +4029,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>T&amp;M Staff Augmentation - AUD - Sales Pipeline</v>
       </c>
-      <c r="H29" t="str">
-        <v>T&amp;M Staff Augmentation - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" hidden="1">
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>101</v>
       </c>
@@ -4150,11 +4050,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Custom Data Analytics Consulting - T&amp;M - AUD - Sales Pipeline</v>
       </c>
-      <c r="H30" t="str">
-        <v>Custom Data Analytics Consulting - T&amp;M - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" hidden="1">
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -4174,11 +4071,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics - Basic Maintenance - AUD - Sales Pipeline</v>
       </c>
-      <c r="H31" t="str">
-        <v>Data Analytics - Basic Maintenance - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" hidden="1">
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>103</v>
       </c>
@@ -4198,11 +4092,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics - Light Managed Service - AUD - Sales Pipeline</v>
       </c>
-      <c r="H32" t="str">
-        <v>Data Analytics - Light Managed Service - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" hidden="1">
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>104</v>
       </c>
@@ -4222,11 +4113,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics - Managed Service - AUD - Sales Pipeline</v>
       </c>
-      <c r="H33" t="str">
-        <v>Data Analytics - Managed Service - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" hidden="1">
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>105</v>
       </c>
@@ -4246,11 +4134,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics - Prototype Model - AUD - Sales Pipeline</v>
       </c>
-      <c r="H34" t="str">
-        <v>Data Analytics - Prototype Model - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>106</v>
       </c>
@@ -4270,11 +4155,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Reseller Monthly Fee - AUD - Reseller Pipeline</v>
       </c>
-      <c r="H35" t="str">
-        <v>Reseller Monthly Fee - AUD - Reseller Pipeline</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>107</v>
       </c>
@@ -4294,11 +4176,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Franchise Setup Fee  - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H36" t="str">
-        <v>Franchise Setup Fee  - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>108</v>
       </c>
@@ -4318,11 +4197,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Lead Gen Tech Stack Fee - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H37" t="str">
-        <v>Monthly Lead Gen Tech Stack Fee - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>109</v>
       </c>
@@ -4342,11 +4218,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Advertisement Fee - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H38" t="str">
-        <v>Monthly Advertisement Fee - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>110</v>
       </c>
@@ -4366,11 +4239,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Support Fee - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H39" t="str">
-        <v>Monthly Support Fee - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>111</v>
       </c>
@@ -4390,11 +4260,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Annual Conference Fee - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H40" t="str">
-        <v>Annual Conference Fee - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>112</v>
       </c>
@@ -4414,11 +4281,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Consultant Access Fee - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H41" t="str">
-        <v>Monthly Consultant Access Fee - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" hidden="1">
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>113</v>
       </c>
@@ -4438,11 +4302,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>COMPLEX - Ai Powered Data Extraction - AUD - Sales Pipeline</v>
       </c>
-      <c r="H42" t="str">
-        <v>COMPLEX - Ai Powered Data Extraction - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1">
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>114</v>
       </c>
@@ -4462,11 +4323,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Ai Powered Data Extraction - AUD - Sales Pipeline</v>
       </c>
-      <c r="H43" t="str">
-        <v>Ai Powered Data Extraction - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" hidden="1">
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>115</v>
       </c>
@@ -4486,11 +4344,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Digital Assistant - upto 250k Executions - AUD - Sales Pipeline</v>
       </c>
-      <c r="H44" t="str">
-        <v>Digital Assistant - upto 250k Executions - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" hidden="1">
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>116</v>
       </c>
@@ -4510,11 +4365,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Digital Assistant - upto 100k Executions - AUD - Sales Pipeline</v>
       </c>
-      <c r="H45" t="str">
-        <v>Digital Assistant - upto 100k Executions - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" hidden="1">
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>117</v>
       </c>
@@ -4534,11 +4386,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Digital Assistant - upto 50k Executions - AUD - Sales Pipeline</v>
       </c>
-      <c r="H46" t="str">
-        <v>Digital Assistant - upto 50k Executions - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" hidden="1">
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>118</v>
       </c>
@@ -4558,11 +4407,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Digital Assistant - upto 10k Executions - AUD - Sales Pipeline</v>
       </c>
-      <c r="H47" t="str">
-        <v>Digital Assistant - upto 10k Executions - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" hidden="1">
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>119</v>
       </c>
@@ -4582,11 +4428,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MSP Reseller - AUD - MSP Pipeline</v>
       </c>
-      <c r="H48" t="str">
-        <v>MSP Reseller - AUD - MSP Pipeline</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" hidden="1">
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>121</v>
       </c>
@@ -4606,11 +4449,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MSP Referral Partner - AUD - MSP Pipeline</v>
       </c>
-      <c r="H49" t="str">
-        <v>MSP Referral Partner - AUD - MSP Pipeline</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" hidden="1">
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>122</v>
       </c>
@@ -4630,11 +4470,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MSP Service Delivery Partner - AUD - MSP Pipeline</v>
       </c>
-      <c r="H50" t="str">
-        <v>MSP Service Delivery Partner - AUD - MSP Pipeline</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" hidden="1">
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>72</v>
       </c>
@@ -4654,11 +4491,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Accountant - NZD - Sales Pipeline</v>
       </c>
-      <c r="H51" t="str">
-        <v>FT Accountant - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" hidden="1">
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>74</v>
       </c>
@@ -4678,11 +4512,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Zoho Developer - NZD - Sales Pipeline</v>
       </c>
-      <c r="H52" t="str">
-        <v>FT Zoho Developer - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" hidden="1">
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>75</v>
       </c>
@@ -4702,11 +4533,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Wealth Management Paraplanner - NZD - Sales Pipeline</v>
       </c>
-      <c r="H53" t="str">
-        <v>PT Wealth Management Paraplanner - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" hidden="1">
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>76</v>
       </c>
@@ -4726,11 +4554,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Salesforce Developer - NZD - Sales Pipeline</v>
       </c>
-      <c r="H54" t="str">
-        <v>FT Salesforce Developer - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" hidden="1">
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -4750,11 +4575,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Wealth Management Paraplanner - NZD - Sales Pipeline</v>
       </c>
-      <c r="H55" t="str">
-        <v>FT Wealth Management Paraplanner - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" hidden="1">
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>78</v>
       </c>
@@ -4774,11 +4596,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Full Stack Developer - NZD - Sales Pipeline</v>
       </c>
-      <c r="H56" t="str">
-        <v>Full Stack Developer - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" hidden="1">
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>79</v>
       </c>
@@ -4798,11 +4617,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Custom Service - NZD - Sales Pipeline</v>
       </c>
-      <c r="H57" t="str">
-        <v>Custom Service - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" hidden="1">
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>80</v>
       </c>
@@ -4822,11 +4638,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Wealth Management Virtual Assistant - NZD - Sales Pipeline</v>
       </c>
-      <c r="H58" t="str">
-        <v>PT Wealth Management Virtual Assistant - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" hidden="1">
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>81</v>
       </c>
@@ -4846,11 +4659,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Bookkeeping - NZD - Sales Pipeline</v>
       </c>
-      <c r="H59" t="str">
-        <v>FT Bookkeeping - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" hidden="1">
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>82</v>
       </c>
@@ -4870,11 +4680,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Oracle HCM Cloud Developer - NZD - Sales Pipeline</v>
       </c>
-      <c r="H60" t="str">
-        <v>Oracle HCM Cloud Developer - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" hidden="1">
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>83</v>
       </c>
@@ -4894,11 +4701,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Zoho Developer - NZD - Sales Pipeline</v>
       </c>
-      <c r="H61" t="str">
-        <v>PT Zoho Developer - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" hidden="1">
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>84</v>
       </c>
@@ -4918,11 +4722,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Full Time Custom Staff Aug - NZD - Sales Pipeline</v>
       </c>
-      <c r="H62" t="str">
-        <v>Full Time Custom Staff Aug - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" hidden="1">
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>85</v>
       </c>
@@ -4942,11 +4743,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Full Time Medical Staff - NZD - Sales Pipeline</v>
       </c>
-      <c r="H63" t="str">
-        <v>Full Time Medical Staff - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" hidden="1">
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>86</v>
       </c>
@@ -4966,11 +4764,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Part Time Custom Staff Aug - NZD - Sales Pipeline</v>
       </c>
-      <c r="H64" t="str">
-        <v>Part Time Custom Staff Aug - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" hidden="1">
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>87</v>
       </c>
@@ -4990,11 +4785,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Accountant - NZD - Sales Pipeline</v>
       </c>
-      <c r="H65" t="str">
-        <v>PT Accountant - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" hidden="1">
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>88</v>
       </c>
@@ -5014,11 +4806,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Wealth Management Virtual Assistant - NZD - Sales Pipeline</v>
       </c>
-      <c r="H66" t="str">
-        <v>FT Wealth Management Virtual Assistant - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" hidden="1">
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>89</v>
       </c>
@@ -5038,11 +4827,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Bookkeeping - NZD - Sales Pipeline</v>
       </c>
-      <c r="H67" t="str">
-        <v>PT Bookkeeping - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" hidden="1">
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>90</v>
       </c>
@@ -5062,11 +4848,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Dedicated 24x7x365 Digital Assistant - NZD - Sales Pipeline</v>
       </c>
-      <c r="H68" t="str">
-        <v>Dedicated 24x7x365 Digital Assistant - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" hidden="1">
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>91</v>
       </c>
@@ -5086,11 +4869,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics Managed Service - NZD - Sales Pipeline</v>
       </c>
-      <c r="H69" t="str">
-        <v>Data Analytics Managed Service - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" hidden="1">
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>92</v>
       </c>
@@ -5110,11 +4890,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics Implementation - NZD - Sales Pipeline</v>
       </c>
-      <c r="H70" t="str">
-        <v>Data Analytics Implementation - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" hidden="1">
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>93</v>
       </c>
@@ -5134,11 +4911,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT RPA Developer - NZD - Sales Pipeline</v>
       </c>
-      <c r="H71" t="str">
-        <v>FT RPA Developer - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" hidden="1">
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>94</v>
       </c>
@@ -5158,11 +4932,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>DA Implementation Team - NZD - Sales Pipeline</v>
       </c>
-      <c r="H72" t="str">
-        <v>DA Implementation Team - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" hidden="1">
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>95</v>
       </c>
@@ -5182,11 +4953,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>AI Data Extraction per page - NZD - Sales Pipeline</v>
       </c>
-      <c r="H73" t="str">
-        <v>AI Data Extraction per page - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" hidden="1">
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>96</v>
       </c>
@@ -5206,11 +4974,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Fractional Digital Assistant - NZD - Sales Pipeline</v>
       </c>
-      <c r="H74" t="str">
-        <v>Fractional Digital Assistant - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" hidden="1">
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>97</v>
       </c>
@@ -5230,11 +4995,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>AI Workshop - NZD - Sales Pipeline</v>
       </c>
-      <c r="H75" t="str">
-        <v>AI Workshop - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>98</v>
       </c>
@@ -5254,11 +5016,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Background Verification Check Fee - NZD - Sales Pipeline</v>
       </c>
-      <c r="H76" t="str">
-        <v>Background Verification Check Fee - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" hidden="1">
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>99</v>
       </c>
@@ -5278,11 +5037,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Onboarding Setup - NZD - Sales Pipeline</v>
       </c>
-      <c r="H77" t="str">
-        <v>Onboarding Setup - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" hidden="1">
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>100</v>
       </c>
@@ -5302,11 +5058,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>T&amp;M Staff Augmentation - NZD - Sales Pipeline</v>
       </c>
-      <c r="H78" t="str">
-        <v>T&amp;M Staff Augmentation - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" hidden="1">
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>101</v>
       </c>
@@ -5326,11 +5079,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Custom Data Analytics Consulting - T&amp;M - NZD - Sales Pipeline</v>
       </c>
-      <c r="H79" t="str">
-        <v>Custom Data Analytics Consulting - T&amp;M - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" hidden="1">
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>102</v>
       </c>
@@ -5350,11 +5100,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics - Basic Maintenance - NZD - Sales Pipeline</v>
       </c>
-      <c r="H80" t="str">
-        <v>Data Analytics - Basic Maintenance - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" hidden="1">
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>103</v>
       </c>
@@ -5374,11 +5121,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics - Light Managed Service - NZD - Sales Pipeline</v>
       </c>
-      <c r="H81" t="str">
-        <v>Data Analytics - Light Managed Service - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" hidden="1">
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>104</v>
       </c>
@@ -5398,11 +5142,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics - Managed Service - NZD - Sales Pipeline</v>
       </c>
-      <c r="H82" t="str">
-        <v>Data Analytics - Managed Service - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" hidden="1">
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>105</v>
       </c>
@@ -5422,11 +5163,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics - Prototype Model - NZD - Sales Pipeline</v>
       </c>
-      <c r="H83" t="str">
-        <v>Data Analytics - Prototype Model - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>106</v>
       </c>
@@ -5446,11 +5184,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Reseller Monthly Fee - NZD - Reseller Pipeline</v>
       </c>
-      <c r="H84" t="str">
-        <v>Reseller Monthly Fee - NZD - Reseller Pipeline</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>107</v>
       </c>
@@ -5470,11 +5205,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Franchise Setup Fee  - NZD - Franchise Pipeline</v>
       </c>
-      <c r="H85" t="str">
-        <v>Franchise Setup Fee  - NZD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>108</v>
       </c>
@@ -5494,11 +5226,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Lead Gen Tech Stack Fee - NZD - Franchise Pipeline</v>
       </c>
-      <c r="H86" t="str">
-        <v>Monthly Lead Gen Tech Stack Fee - NZD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>109</v>
       </c>
@@ -5518,11 +5247,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Advertisement Fee - NZD - Franchise Pipeline</v>
       </c>
-      <c r="H87" t="str">
-        <v>Monthly Advertisement Fee - NZD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>110</v>
       </c>
@@ -5542,11 +5268,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Support Fee - NZD - Franchise Pipeline</v>
       </c>
-      <c r="H88" t="str">
-        <v>Monthly Support Fee - NZD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>111</v>
       </c>
@@ -5566,11 +5289,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Annual Conference Fee - NZD - Franchise Pipeline</v>
       </c>
-      <c r="H89" t="str">
-        <v>Annual Conference Fee - NZD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>112</v>
       </c>
@@ -5590,11 +5310,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Consultant Access Fee - NZD - Franchise Pipeline</v>
       </c>
-      <c r="H90" t="str">
-        <v>Monthly Consultant Access Fee - NZD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" hidden="1">
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>113</v>
       </c>
@@ -5614,11 +5331,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>COMPLEX - Ai Powered Data Extraction - NZD - Sales Pipeline</v>
       </c>
-      <c r="H91" t="str">
-        <v>COMPLEX - Ai Powered Data Extraction - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" hidden="1">
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>114</v>
       </c>
@@ -5638,11 +5352,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Ai Powered Data Extraction - NZD - Sales Pipeline</v>
       </c>
-      <c r="H92" t="str">
-        <v>Ai Powered Data Extraction - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" hidden="1">
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>115</v>
       </c>
@@ -5662,11 +5373,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Digital Assistant - upto 250k Executions - NZD - Sales Pipeline</v>
       </c>
-      <c r="H93" t="str">
-        <v>Digital Assistant - upto 250k Executions - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" hidden="1">
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>116</v>
       </c>
@@ -5686,11 +5394,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Digital Assistant - upto 100k Executions - NZD - Sales Pipeline</v>
       </c>
-      <c r="H94" t="str">
-        <v>Digital Assistant - upto 100k Executions - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" hidden="1">
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>117</v>
       </c>
@@ -5710,11 +5415,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Digital Assistant - upto 50k Executions - NZD - Sales Pipeline</v>
       </c>
-      <c r="H95" t="str">
-        <v>Digital Assistant - upto 50k Executions - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" hidden="1">
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>118</v>
       </c>
@@ -5734,11 +5436,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Digital Assistant - upto 10k Executions - NZD - Sales Pipeline</v>
       </c>
-      <c r="H96" t="str">
-        <v>Digital Assistant - upto 10k Executions - NZD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" hidden="1">
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>119</v>
       </c>
@@ -5758,11 +5457,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MSP Reseller - NZD - MSP Pipeline</v>
       </c>
-      <c r="H97" t="str">
-        <v>MSP Reseller - NZD - MSP Pipeline</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" hidden="1">
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>121</v>
       </c>
@@ -5782,11 +5478,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MSP Referral Partner - NZD - MSP Pipeline</v>
       </c>
-      <c r="H98" t="str">
-        <v>MSP Referral Partner - NZD - MSP Pipeline</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" hidden="1">
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>122</v>
       </c>
@@ -5806,11 +5499,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MSP Service Delivery Partner - NZD - MSP Pipeline</v>
       </c>
-      <c r="H99" t="str">
-        <v>MSP Service Delivery Partner - NZD - MSP Pipeline</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" hidden="1">
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>72</v>
       </c>
@@ -5830,11 +5520,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Accountant - GBP - Sales Pipeline</v>
       </c>
-      <c r="H100" t="str">
-        <v>FT Accountant - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" hidden="1">
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>74</v>
       </c>
@@ -5854,11 +5541,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Zoho Developer - GBP - Sales Pipeline</v>
       </c>
-      <c r="H101" t="str">
-        <v>FT Zoho Developer - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" hidden="1">
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>75</v>
       </c>
@@ -5878,11 +5562,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Wealth Management Paraplanner - GBP - Sales Pipeline</v>
       </c>
-      <c r="H102" t="str">
-        <v>PT Wealth Management Paraplanner - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" hidden="1">
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>76</v>
       </c>
@@ -5902,11 +5583,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Salesforce Developer - GBP - Sales Pipeline</v>
       </c>
-      <c r="H103" t="str">
-        <v>FT Salesforce Developer - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" hidden="1">
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>77</v>
       </c>
@@ -5926,11 +5604,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Wealth Management Paraplanner - GBP - Sales Pipeline</v>
       </c>
-      <c r="H104" t="str">
-        <v>FT Wealth Management Paraplanner - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" hidden="1">
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>78</v>
       </c>
@@ -5950,11 +5625,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Full Stack Developer - GBP - Sales Pipeline</v>
       </c>
-      <c r="H105" t="str">
-        <v>Full Stack Developer - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" hidden="1">
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>79</v>
       </c>
@@ -5974,11 +5646,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Custom Service - GBP - Sales Pipeline</v>
       </c>
-      <c r="H106" t="str">
-        <v>Custom Service - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" hidden="1">
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>80</v>
       </c>
@@ -5998,11 +5667,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Wealth Management Virtual Assistant - GBP - Sales Pipeline</v>
       </c>
-      <c r="H107" t="str">
-        <v>PT Wealth Management Virtual Assistant - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" hidden="1">
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>81</v>
       </c>
@@ -6022,11 +5688,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Bookkeeping - GBP - Sales Pipeline</v>
       </c>
-      <c r="H108" t="str">
-        <v>FT Bookkeeping - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" hidden="1">
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>82</v>
       </c>
@@ -6046,11 +5709,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Oracle HCM Cloud Developer - GBP - Sales Pipeline</v>
       </c>
-      <c r="H109" t="str">
-        <v>Oracle HCM Cloud Developer - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" hidden="1">
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>83</v>
       </c>
@@ -6070,11 +5730,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Zoho Developer - GBP - Sales Pipeline</v>
       </c>
-      <c r="H110" t="str">
-        <v>PT Zoho Developer - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" hidden="1">
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>84</v>
       </c>
@@ -6094,11 +5751,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Full Time Custom Staff Aug - GBP - Sales Pipeline</v>
       </c>
-      <c r="H111" t="str">
-        <v>Full Time Custom Staff Aug - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" hidden="1">
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>85</v>
       </c>
@@ -6118,11 +5772,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Full Time Medical Staff - GBP - Sales Pipeline</v>
       </c>
-      <c r="H112" t="str">
-        <v>Full Time Medical Staff - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" hidden="1">
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>86</v>
       </c>
@@ -6142,11 +5793,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Part Time Custom Staff Aug - GBP - Sales Pipeline</v>
       </c>
-      <c r="H113" t="str">
-        <v>Part Time Custom Staff Aug - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" hidden="1">
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>87</v>
       </c>
@@ -6166,11 +5814,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Accountant - GBP - Sales Pipeline</v>
       </c>
-      <c r="H114" t="str">
-        <v>PT Accountant - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" hidden="1">
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>88</v>
       </c>
@@ -6190,11 +5835,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT Wealth Management Virtual Assistant - GBP - Sales Pipeline</v>
       </c>
-      <c r="H115" t="str">
-        <v>FT Wealth Management Virtual Assistant - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" hidden="1">
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>89</v>
       </c>
@@ -6214,11 +5856,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>PT Bookkeeping - GBP - Sales Pipeline</v>
       </c>
-      <c r="H116" t="str">
-        <v>PT Bookkeeping - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" hidden="1">
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>90</v>
       </c>
@@ -6238,11 +5877,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Dedicated 24x7x365 Digital Assistant - GBP - Sales Pipeline</v>
       </c>
-      <c r="H117" t="str">
-        <v>Dedicated 24x7x365 Digital Assistant - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" hidden="1">
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>91</v>
       </c>
@@ -6262,11 +5898,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics Managed Service - GBP - Sales Pipeline</v>
       </c>
-      <c r="H118" t="str">
-        <v>Data Analytics Managed Service - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" hidden="1">
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>92</v>
       </c>
@@ -6286,11 +5919,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics Implementation - GBP - Sales Pipeline</v>
       </c>
-      <c r="H119" t="str">
-        <v>Data Analytics Implementation - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" hidden="1">
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>93</v>
       </c>
@@ -6310,11 +5940,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>FT RPA Developer - GBP - Sales Pipeline</v>
       </c>
-      <c r="H120" t="str">
-        <v>FT RPA Developer - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" hidden="1">
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>94</v>
       </c>
@@ -6334,11 +5961,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>DA Implementation Team - GBP - Sales Pipeline</v>
       </c>
-      <c r="H121" t="str">
-        <v>DA Implementation Team - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" hidden="1">
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>95</v>
       </c>
@@ -6358,11 +5982,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>AI Data Extraction per page - GBP - Sales Pipeline</v>
       </c>
-      <c r="H122" t="str">
-        <v>AI Data Extraction per page - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" hidden="1">
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>96</v>
       </c>
@@ -6382,11 +6003,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Fractional Digital Assistant - GBP - Sales Pipeline</v>
       </c>
-      <c r="H123" t="str">
-        <v>Fractional Digital Assistant - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" hidden="1">
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>97</v>
       </c>
@@ -6406,11 +6024,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>AI Workshop - GBP - Sales Pipeline</v>
       </c>
-      <c r="H124" t="str">
-        <v>AI Workshop - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>98</v>
       </c>
@@ -6430,11 +6045,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Background Verification Check Fee - GBP - Sales Pipeline</v>
       </c>
-      <c r="H125" t="str">
-        <v>Background Verification Check Fee - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" hidden="1">
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>99</v>
       </c>
@@ -6454,11 +6066,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Onboarding Setup - GBP - Sales Pipeline</v>
       </c>
-      <c r="H126" t="str">
-        <v>Onboarding Setup - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" hidden="1">
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>100</v>
       </c>
@@ -6478,11 +6087,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>T&amp;M Staff Augmentation - GBP - Sales Pipeline</v>
       </c>
-      <c r="H127" t="str">
-        <v>T&amp;M Staff Augmentation - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" hidden="1">
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>101</v>
       </c>
@@ -6502,11 +6108,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Custom Data Analytics Consulting - T&amp;M - GBP - Sales Pipeline</v>
       </c>
-      <c r="H128" t="str">
-        <v>Custom Data Analytics Consulting - T&amp;M - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" hidden="1">
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>102</v>
       </c>
@@ -6526,11 +6129,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics - Basic Maintenance - GBP - Sales Pipeline</v>
       </c>
-      <c r="H129" t="str">
-        <v>Data Analytics - Basic Maintenance - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" hidden="1">
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>103</v>
       </c>
@@ -6550,11 +6150,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics - Light Managed Service - GBP - Sales Pipeline</v>
       </c>
-      <c r="H130" t="str">
-        <v>Data Analytics - Light Managed Service - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" hidden="1">
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>104</v>
       </c>
@@ -6574,11 +6171,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics - Managed Service - GBP - Sales Pipeline</v>
       </c>
-      <c r="H131" t="str">
-        <v>Data Analytics - Managed Service - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" hidden="1">
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>105</v>
       </c>
@@ -6598,11 +6192,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analytics - Prototype Model - GBP - Sales Pipeline</v>
       </c>
-      <c r="H132" t="str">
-        <v>Data Analytics - Prototype Model - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>106</v>
       </c>
@@ -6622,11 +6213,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Reseller Monthly Fee - GBP - Reseller Pipeline</v>
       </c>
-      <c r="H133" t="str">
-        <v>Reseller Monthly Fee - GBP - Reseller Pipeline</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8">
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>107</v>
       </c>
@@ -6646,11 +6234,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Franchise Setup Fee  - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H134" t="str">
-        <v>Franchise Setup Fee  - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8">
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
         <v>108</v>
       </c>
@@ -6670,11 +6255,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Lead Gen Tech Stack Fee - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H135" t="str">
-        <v>Monthly Lead Gen Tech Stack Fee - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
         <v>109</v>
       </c>
@@ -6694,11 +6276,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Advertisement Fee - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H136" t="str">
-        <v>Monthly Advertisement Fee - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8">
+    </row>
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
         <v>110</v>
       </c>
@@ -6718,11 +6297,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Support Fee - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H137" t="str">
-        <v>Monthly Support Fee - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8">
+    </row>
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>111</v>
       </c>
@@ -6742,11 +6318,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Annual Conference Fee - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H138" t="str">
-        <v>Annual Conference Fee - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8">
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>112</v>
       </c>
@@ -6766,11 +6339,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Consultant Access Fee - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H139" t="str">
-        <v>Monthly Consultant Access Fee - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" hidden="1">
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>113</v>
       </c>
@@ -6790,11 +6360,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>COMPLEX - Ai Powered Data Extraction - GBP - Sales Pipeline</v>
       </c>
-      <c r="H140" t="str">
-        <v>COMPLEX - Ai Powered Data Extraction - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" hidden="1">
+    </row>
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>114</v>
       </c>
@@ -6814,11 +6381,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Ai Powered Data Extraction - GBP - Sales Pipeline</v>
       </c>
-      <c r="H141" t="str">
-        <v>Ai Powered Data Extraction - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" hidden="1">
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>115</v>
       </c>
@@ -6838,11 +6402,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Digital Assistant - upto 250k Executions - GBP - Sales Pipeline</v>
       </c>
-      <c r="H142" t="str">
-        <v>Digital Assistant - upto 250k Executions - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" hidden="1">
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>116</v>
       </c>
@@ -6862,11 +6423,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Digital Assistant - upto 100k Executions - GBP - Sales Pipeline</v>
       </c>
-      <c r="H143" t="str">
-        <v>Digital Assistant - upto 100k Executions - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" hidden="1">
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
         <v>117</v>
       </c>
@@ -6886,11 +6444,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Digital Assistant - upto 50k Executions - GBP - Sales Pipeline</v>
       </c>
-      <c r="H144" t="str">
-        <v>Digital Assistant - upto 50k Executions - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" hidden="1">
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>118</v>
       </c>
@@ -6910,11 +6465,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Digital Assistant - upto 10k Executions - GBP - Sales Pipeline</v>
       </c>
-      <c r="H145" t="str">
-        <v>Digital Assistant - upto 10k Executions - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" hidden="1">
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>119</v>
       </c>
@@ -6934,11 +6486,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MSP Reseller - GBP - MSP Pipeline</v>
       </c>
-      <c r="H146" t="str">
-        <v>MSP Reseller - GBP - MSP Pipeline</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" hidden="1">
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
         <v>121</v>
       </c>
@@ -6958,11 +6507,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MSP Referral Partner - GBP - MSP Pipeline</v>
       </c>
-      <c r="H147" t="str">
-        <v>MSP Referral Partner - GBP - MSP Pipeline</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" hidden="1">
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
         <v>122</v>
       </c>
@@ -6982,11 +6528,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MSP Service Delivery Partner - GBP - MSP Pipeline</v>
       </c>
-      <c r="H148" t="str">
-        <v>MSP Service Delivery Partner - GBP - MSP Pipeline</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" hidden="1">
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
         <v>126</v>
       </c>
@@ -7006,11 +6549,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - Dripify License - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H149" t="str">
-        <v>Consultant - Dripify License - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" hidden="1">
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" t="s">
         <v>127</v>
       </c>
@@ -7030,11 +6570,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>1Password License - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H150" t="str">
-        <v>1Password License - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" hidden="1">
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
         <v>128</v>
       </c>
@@ -7054,11 +6591,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS Email Only + 1Password - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H151" t="str">
-        <v>Consultant - MS Email Only + 1Password - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" hidden="1">
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
         <v>129</v>
       </c>
@@ -7078,11 +6612,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - HubSpot Sales License - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H152" t="str">
-        <v>Consultant - HubSpot Sales License - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" hidden="1">
+    </row>
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
         <v>130</v>
       </c>
@@ -7102,11 +6633,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS CoPilot License - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H153" t="str">
-        <v>Consultant - MS CoPilot License - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" hidden="1">
+    </row>
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
         <v>131</v>
       </c>
@@ -7126,11 +6654,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>HubSpot Sales License - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H154" t="str">
-        <v>HubSpot Sales License - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" hidden="1">
+    </row>
+    <row r="155" spans="1:6">
       <c r="A155" t="s">
         <v>132</v>
       </c>
@@ -7150,11 +6675,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - Apollo License - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H155" t="str">
-        <v>Consultant - Apollo License - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" hidden="1">
+    </row>
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
         <v>133</v>
       </c>
@@ -7174,11 +6696,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS Email Only - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H156" t="str">
-        <v>Consultant - MS Email Only - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" hidden="1">
+    </row>
+    <row r="157" spans="1:6">
       <c r="A157" t="s">
         <v>134</v>
       </c>
@@ -7198,11 +6717,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS O365 License + 1Password - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H157" t="str">
-        <v>Consultant - MS O365 License + 1Password - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" hidden="1">
+    </row>
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
         <v>135</v>
       </c>
@@ -7222,11 +6738,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Dripify License - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H158" t="str">
-        <v>Dripify License - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8">
+    </row>
+    <row r="159" spans="1:6">
       <c r="A159" t="s">
         <v>136</v>
       </c>
@@ -7246,11 +6759,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Annual Conference Fee - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H159" t="str">
-        <v>Monthly Annual Conference Fee - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" hidden="1">
+    </row>
+    <row r="160" spans="1:6">
       <c r="A160" t="s">
         <v>137</v>
       </c>
@@ -7270,11 +6780,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MS CoPilot License - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H160" t="str">
-        <v>MS CoPilot License - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" hidden="1">
+    </row>
+    <row r="161" spans="1:6">
       <c r="A161" t="s">
         <v>138</v>
       </c>
@@ -7294,11 +6801,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MS O365 License + 1Password - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H161" t="str">
-        <v>MS O365 License + 1Password - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" hidden="1">
+    </row>
+    <row r="162" spans="1:6">
       <c r="A162" t="s">
         <v>139</v>
       </c>
@@ -7318,11 +6822,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Apollo License - AUD - Franchise Pipeline</v>
       </c>
-      <c r="H162" t="str">
-        <v>Apollo License - AUD - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" hidden="1">
+    </row>
+    <row r="163" spans="1:6">
       <c r="A163" t="s">
         <v>140</v>
       </c>
@@ -7342,11 +6843,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analyst - AUD - Sales Pipeline</v>
       </c>
-      <c r="H163" t="str">
-        <v>Data Analyst - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" hidden="1">
+    </row>
+    <row r="164" spans="1:6">
       <c r="A164" t="s">
         <v>141</v>
       </c>
@@ -7366,11 +6864,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Reseller International - AUD - Reseller Pipeline</v>
       </c>
-      <c r="H164" t="str">
-        <v>Reseller International - AUD - Reseller Pipeline</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8">
+    </row>
+    <row r="165" spans="1:6">
       <c r="A165" t="s">
         <v>106</v>
       </c>
@@ -7390,11 +6885,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Reseller Monthly Fee - AUD - Reseller Pipeline</v>
       </c>
-      <c r="H165" t="str">
-        <v>Consultant - Dripify License - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" hidden="1">
+    </row>
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
         <v>126</v>
       </c>
@@ -7414,11 +6906,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - Dripify License - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H166" t="str">
-        <v>1Password License - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" hidden="1">
+    </row>
+    <row r="167" spans="1:6">
       <c r="A167" t="s">
         <v>127</v>
       </c>
@@ -7438,11 +6927,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>1Password License - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H167" t="str">
-        <v>Consultant - MS Email Only + 1Password - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" hidden="1">
+    </row>
+    <row r="168" spans="1:6">
       <c r="A168" t="s">
         <v>128</v>
       </c>
@@ -7462,11 +6948,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS Email Only + 1Password - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H168" t="str">
-        <v>Consultant - HubSpot Sales License - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" hidden="1">
+    </row>
+    <row r="169" spans="1:6">
       <c r="A169" t="s">
         <v>129</v>
       </c>
@@ -7486,11 +6969,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - HubSpot Sales License - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H169" t="str">
-        <v>Consultant - MS CoPilot License - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" hidden="1">
+    </row>
+    <row r="170" spans="1:6">
       <c r="A170" t="s">
         <v>130</v>
       </c>
@@ -7510,11 +6990,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS CoPilot License - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H170" t="str">
-        <v>HubSpot Sales License - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" hidden="1">
+    </row>
+    <row r="171" spans="1:6">
       <c r="A171" t="s">
         <v>131</v>
       </c>
@@ -7534,11 +7011,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>HubSpot Sales License - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H171" t="str">
-        <v>Consultant - Apollo License - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" hidden="1">
+    </row>
+    <row r="172" spans="1:6">
       <c r="A172" t="s">
         <v>132</v>
       </c>
@@ -7558,11 +7032,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - Apollo License - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H172" t="str">
-        <v>Consultant - MS Email Only - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" hidden="1">
+    </row>
+    <row r="173" spans="1:6">
       <c r="A173" t="s">
         <v>133</v>
       </c>
@@ -7582,11 +7053,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS Email Only - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H173" t="str">
-        <v>Consultant - MS O365 License + 1Password - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" hidden="1">
+    </row>
+    <row r="174" spans="1:6">
       <c r="A174" t="s">
         <v>134</v>
       </c>
@@ -7606,11 +7074,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Consultant - MS O365 License + 1Password - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H174" t="str">
-        <v>Dripify License - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" hidden="1">
+    </row>
+    <row r="175" spans="1:6">
       <c r="A175" t="s">
         <v>135</v>
       </c>
@@ -7630,11 +7095,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Dripify License - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H175" t="str">
-        <v>Monthly Annual Conference Fee - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8">
+    </row>
+    <row r="176" spans="1:6">
       <c r="A176" t="s">
         <v>136</v>
       </c>
@@ -7654,11 +7116,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Monthly Annual Conference Fee - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H176" t="str">
-        <v>MS CoPilot License - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8" hidden="1">
+    </row>
+    <row r="177" spans="1:6">
       <c r="A177" t="s">
         <v>137</v>
       </c>
@@ -7678,11 +7137,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MS CoPilot License - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H177" t="str">
-        <v>MS O365 License + 1Password - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" hidden="1">
+    </row>
+    <row r="178" spans="1:6">
       <c r="A178" t="s">
         <v>138</v>
       </c>
@@ -7702,11 +7158,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>MS O365 License + 1Password - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H178" t="str">
-        <v>Apollo License - GBP - Franchise Pipeline</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" hidden="1">
+    </row>
+    <row r="179" spans="1:6">
       <c r="A179" t="s">
         <v>139</v>
       </c>
@@ -7726,11 +7179,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Apollo License - GBP - Franchise Pipeline</v>
       </c>
-      <c r="H179" t="str">
-        <v>Data Analyst - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" hidden="1">
+    </row>
+    <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>140</v>
       </c>
@@ -7750,11 +7200,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Data Analyst - GBP - Sales Pipeline</v>
       </c>
-      <c r="H180" t="str">
-        <v>Reseller International - GBP - Reseller Pipeline</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" hidden="1">
+    </row>
+    <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>141</v>
       </c>
@@ -7774,11 +7221,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Reseller International - GBP - Reseller Pipeline</v>
       </c>
-      <c r="H181" t="str">
-        <v>Client Staff Bonus - AUD - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8" hidden="1">
+    </row>
+    <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>142</v>
       </c>
@@ -7798,11 +7242,8 @@
         <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
         <v>Client Staff Bonus - AUD - Sales Pipeline</v>
       </c>
-      <c r="H182" t="str">
-        <v>Client Staff Bonus - GBP - Sales Pipeline</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8" hidden="1">
+    </row>
+    <row r="183" spans="1:6">
       <c r="A183" t="s">
         <v>142</v>
       </c>

--- a/Data/Temp/InvoicesReport UI Extraction.xlsx
+++ b/Data/Temp/InvoicesReport UI Extraction.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanielRicardoRochaQu\Downloads\Invoicing Bot\Recon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1220" documentId="13_ncr:1_{B5D6CEAF-E681-4588-8E6E-EF4492DB7BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AA67935-33BF-47B8-AAB6-FA2AAFFD4CAE}"/>
+  <xr:revisionPtr revIDLastSave="1221" documentId="13_ncr:1_{B5D6CEAF-E681-4588-8E6E-EF4492DB7BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1E9BAF7-DFE4-4C3B-83CC-F19F6A125004}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="6" xr2:uid="{70E8A791-13CE-4BD4-B2C5-703777F4F9B6}"/>
   </bookViews>
@@ -1407,13 +1407,7 @@
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}" name="Xero_Tax_Acc" displayName="Xero_Tax_Acc" ref="A1:F185" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:F185" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Monthly Support Fee"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F185" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{ADF06759-72AB-4C84-B20B-0E8D66CF7A70}" name="Line Item"/>
     <tableColumn id="4" xr3:uid="{136FB1F1-5689-4097-ACD2-3191F8E3FAEA}" name="Currency"/>
@@ -3451,7 +3445,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -3472,7 +3466,7 @@
         <v>FT Accountant - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -3493,7 +3487,7 @@
         <v>FT Zoho Developer - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -3514,7 +3508,7 @@
         <v>PT Wealth Management Paraplanner - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -3535,7 +3529,7 @@
         <v>FT Salesforce Developer - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -3556,7 +3550,7 @@
         <v>FT Wealth Management Paraplanner - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -3577,7 +3571,7 @@
         <v>Full Stack Developer - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -3598,7 +3592,7 @@
         <v>Custom Service - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -3619,7 +3613,7 @@
         <v>PT Wealth Management Virtual Assistant - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>81</v>
       </c>
@@ -3640,7 +3634,7 @@
         <v>FT Bookkeeping - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -3661,7 +3655,7 @@
         <v>Oracle HCM Cloud Developer - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>83</v>
       </c>
@@ -3682,7 +3676,7 @@
         <v>PT Zoho Developer - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -3703,7 +3697,7 @@
         <v>Full Time Custom Staff Aug - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>85</v>
       </c>
@@ -3724,7 +3718,7 @@
         <v>Full Time Medical Staff - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -3745,7 +3739,7 @@
         <v>Part Time Custom Staff Aug - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>87</v>
       </c>
@@ -3766,7 +3760,7 @@
         <v>PT Accountant - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -3787,7 +3781,7 @@
         <v>FT Wealth Management Virtual Assistant - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -3808,7 +3802,7 @@
         <v>PT Bookkeeping - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>90</v>
       </c>
@@ -3829,7 +3823,7 @@
         <v>Dedicated 24x7x365 Digital Assistant - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -3850,7 +3844,7 @@
         <v>Data Analytics Managed Service - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -3871,7 +3865,7 @@
         <v>Data Analytics Implementation - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>93</v>
       </c>
@@ -3892,7 +3886,7 @@
         <v>FT RPA Developer - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -3913,7 +3907,7 @@
         <v>DA Implementation Team - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>95</v>
       </c>
@@ -3934,7 +3928,7 @@
         <v>AI Data Extraction per page - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>96</v>
       </c>
@@ -3955,7 +3949,7 @@
         <v>Fractional Digital Assistant - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>97</v>
       </c>
@@ -3976,7 +3970,7 @@
         <v>AI Workshop - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -3997,7 +3991,7 @@
         <v>Background Verification Check Fee - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>99</v>
       </c>
@@ -4018,7 +4012,7 @@
         <v>Onboarding Setup - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>100</v>
       </c>
@@ -4039,7 +4033,7 @@
         <v>T&amp;M Staff Augmentation - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>101</v>
       </c>
@@ -4060,7 +4054,7 @@
         <v>Custom Data Analytics Consulting - T&amp;M - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -4081,7 +4075,7 @@
         <v>Data Analytics - Basic Maintenance - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>103</v>
       </c>
@@ -4102,7 +4096,7 @@
         <v>Data Analytics - Light Managed Service - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>104</v>
       </c>
@@ -4123,7 +4117,7 @@
         <v>Data Analytics - Managed Service - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>105</v>
       </c>
@@ -4144,7 +4138,7 @@
         <v>Data Analytics - Prototype Model - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>106</v>
       </c>
@@ -4165,7 +4159,7 @@
         <v>Reseller Monthly Fee - AUD - Reseller Pipeline</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>107</v>
       </c>
@@ -4186,7 +4180,7 @@
         <v>Franchise Setup Fee  - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>108</v>
       </c>
@@ -4207,7 +4201,7 @@
         <v>Monthly Lead Gen Tech Stack Fee - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>109</v>
       </c>
@@ -4249,7 +4243,7 @@
         <v>Monthly Support Fee - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>111</v>
       </c>
@@ -4270,7 +4264,7 @@
         <v>Annual Conference Fee - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>112</v>
       </c>
@@ -4291,7 +4285,7 @@
         <v>Monthly Consultant Access Fee - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>113</v>
       </c>
@@ -4312,7 +4306,7 @@
         <v>COMPLEX - Ai Powered Data Extraction - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>114</v>
       </c>
@@ -4333,7 +4327,7 @@
         <v>Ai Powered Data Extraction - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>115</v>
       </c>
@@ -4354,7 +4348,7 @@
         <v>Digital Assistant - upto 250k Executions - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>116</v>
       </c>
@@ -4375,7 +4369,7 @@
         <v>Digital Assistant - upto 100k Executions - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>117</v>
       </c>
@@ -4396,7 +4390,7 @@
         <v>Digital Assistant - upto 50k Executions - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>118</v>
       </c>
@@ -4417,7 +4411,7 @@
         <v>Digital Assistant - upto 10k Executions - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>119</v>
       </c>
@@ -4438,7 +4432,7 @@
         <v>MSP Reseller - AUD - MSP Pipeline</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>121</v>
       </c>
@@ -4459,7 +4453,7 @@
         <v>MSP Referral Partner - AUD - MSP Pipeline</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>122</v>
       </c>
@@ -4480,7 +4474,7 @@
         <v>MSP Service Delivery Partner - AUD - MSP Pipeline</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>72</v>
       </c>
@@ -4501,7 +4495,7 @@
         <v>FT Accountant - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>74</v>
       </c>
@@ -4522,7 +4516,7 @@
         <v>FT Zoho Developer - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>75</v>
       </c>
@@ -4543,7 +4537,7 @@
         <v>PT Wealth Management Paraplanner - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>76</v>
       </c>
@@ -4564,7 +4558,7 @@
         <v>FT Salesforce Developer - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -4585,7 +4579,7 @@
         <v>FT Wealth Management Paraplanner - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>78</v>
       </c>
@@ -4606,7 +4600,7 @@
         <v>Full Stack Developer - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>79</v>
       </c>
@@ -4627,7 +4621,7 @@
         <v>Custom Service - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>80</v>
       </c>
@@ -4648,7 +4642,7 @@
         <v>PT Wealth Management Virtual Assistant - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>81</v>
       </c>
@@ -4669,7 +4663,7 @@
         <v>FT Bookkeeping - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>82</v>
       </c>
@@ -4690,7 +4684,7 @@
         <v>Oracle HCM Cloud Developer - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>83</v>
       </c>
@@ -4711,7 +4705,7 @@
         <v>PT Zoho Developer - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>84</v>
       </c>
@@ -4732,7 +4726,7 @@
         <v>Full Time Custom Staff Aug - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>85</v>
       </c>
@@ -4753,7 +4747,7 @@
         <v>Full Time Medical Staff - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>86</v>
       </c>
@@ -4774,7 +4768,7 @@
         <v>Part Time Custom Staff Aug - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>87</v>
       </c>
@@ -4795,7 +4789,7 @@
         <v>PT Accountant - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>88</v>
       </c>
@@ -4816,7 +4810,7 @@
         <v>FT Wealth Management Virtual Assistant - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>89</v>
       </c>
@@ -4837,7 +4831,7 @@
         <v>PT Bookkeeping - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>90</v>
       </c>
@@ -4858,7 +4852,7 @@
         <v>Dedicated 24x7x365 Digital Assistant - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>91</v>
       </c>
@@ -4879,7 +4873,7 @@
         <v>Data Analytics Managed Service - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>92</v>
       </c>
@@ -4900,7 +4894,7 @@
         <v>Data Analytics Implementation - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>93</v>
       </c>
@@ -4921,7 +4915,7 @@
         <v>FT RPA Developer - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>94</v>
       </c>
@@ -4942,7 +4936,7 @@
         <v>DA Implementation Team - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>95</v>
       </c>
@@ -4963,7 +4957,7 @@
         <v>AI Data Extraction per page - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>96</v>
       </c>
@@ -4984,7 +4978,7 @@
         <v>Fractional Digital Assistant - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>97</v>
       </c>
@@ -5005,7 +4999,7 @@
         <v>AI Workshop - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="76" spans="1:6" hidden="1">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>98</v>
       </c>
@@ -5026,7 +5020,7 @@
         <v>Background Verification Check Fee - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>99</v>
       </c>
@@ -5047,7 +5041,7 @@
         <v>Onboarding Setup - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="78" spans="1:6" hidden="1">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>100</v>
       </c>
@@ -5068,7 +5062,7 @@
         <v>T&amp;M Staff Augmentation - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>101</v>
       </c>
@@ -5089,7 +5083,7 @@
         <v>Custom Data Analytics Consulting - T&amp;M - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>102</v>
       </c>
@@ -5110,7 +5104,7 @@
         <v>Data Analytics - Basic Maintenance - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>103</v>
       </c>
@@ -5131,7 +5125,7 @@
         <v>Data Analytics - Light Managed Service - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="82" spans="1:6" hidden="1">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>104</v>
       </c>
@@ -5152,7 +5146,7 @@
         <v>Data Analytics - Managed Service - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="83" spans="1:6" hidden="1">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>105</v>
       </c>
@@ -5173,7 +5167,7 @@
         <v>Data Analytics - Prototype Model - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="84" spans="1:6" hidden="1">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>106</v>
       </c>
@@ -5194,7 +5188,7 @@
         <v>Reseller Monthly Fee - NZD - Reseller Pipeline</v>
       </c>
     </row>
-    <row r="85" spans="1:6" hidden="1">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>107</v>
       </c>
@@ -5215,7 +5209,7 @@
         <v>Franchise Setup Fee  - NZD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="86" spans="1:6" hidden="1">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>108</v>
       </c>
@@ -5236,7 +5230,7 @@
         <v>Monthly Lead Gen Tech Stack Fee - NZD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="87" spans="1:6" hidden="1">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>109</v>
       </c>
@@ -5278,7 +5272,7 @@
         <v>Monthly Support Fee - NZD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="89" spans="1:6" hidden="1">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>111</v>
       </c>
@@ -5299,7 +5293,7 @@
         <v>Annual Conference Fee - NZD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="90" spans="1:6" hidden="1">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>112</v>
       </c>
@@ -5320,7 +5314,7 @@
         <v>Monthly Consultant Access Fee - NZD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="91" spans="1:6" hidden="1">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>113</v>
       </c>
@@ -5341,7 +5335,7 @@
         <v>COMPLEX - Ai Powered Data Extraction - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="92" spans="1:6" hidden="1">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>114</v>
       </c>
@@ -5362,7 +5356,7 @@
         <v>Ai Powered Data Extraction - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="93" spans="1:6" hidden="1">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>115</v>
       </c>
@@ -5383,7 +5377,7 @@
         <v>Digital Assistant - upto 250k Executions - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="94" spans="1:6" hidden="1">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>116</v>
       </c>
@@ -5404,7 +5398,7 @@
         <v>Digital Assistant - upto 100k Executions - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="95" spans="1:6" hidden="1">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>117</v>
       </c>
@@ -5425,7 +5419,7 @@
         <v>Digital Assistant - upto 50k Executions - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="96" spans="1:6" hidden="1">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>118</v>
       </c>
@@ -5446,7 +5440,7 @@
         <v>Digital Assistant - upto 10k Executions - NZD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="97" spans="1:6" hidden="1">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>119</v>
       </c>
@@ -5467,7 +5461,7 @@
         <v>MSP Reseller - NZD - MSP Pipeline</v>
       </c>
     </row>
-    <row r="98" spans="1:6" hidden="1">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>121</v>
       </c>
@@ -5488,7 +5482,7 @@
         <v>MSP Referral Partner - NZD - MSP Pipeline</v>
       </c>
     </row>
-    <row r="99" spans="1:6" hidden="1">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>122</v>
       </c>
@@ -5509,7 +5503,7 @@
         <v>MSP Service Delivery Partner - NZD - MSP Pipeline</v>
       </c>
     </row>
-    <row r="100" spans="1:6" hidden="1">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>72</v>
       </c>
@@ -5530,7 +5524,7 @@
         <v>FT Accountant - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="101" spans="1:6" hidden="1">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>74</v>
       </c>
@@ -5551,7 +5545,7 @@
         <v>FT Zoho Developer - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="102" spans="1:6" hidden="1">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>75</v>
       </c>
@@ -5572,7 +5566,7 @@
         <v>PT Wealth Management Paraplanner - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="103" spans="1:6" hidden="1">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>76</v>
       </c>
@@ -5593,7 +5587,7 @@
         <v>FT Salesforce Developer - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="104" spans="1:6" hidden="1">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>77</v>
       </c>
@@ -5614,7 +5608,7 @@
         <v>FT Wealth Management Paraplanner - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="105" spans="1:6" hidden="1">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>78</v>
       </c>
@@ -5635,7 +5629,7 @@
         <v>Full Stack Developer - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="106" spans="1:6" hidden="1">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>79</v>
       </c>
@@ -5656,7 +5650,7 @@
         <v>Custom Service - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="107" spans="1:6" hidden="1">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>80</v>
       </c>
@@ -5677,7 +5671,7 @@
         <v>PT Wealth Management Virtual Assistant - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="108" spans="1:6" hidden="1">
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>81</v>
       </c>
@@ -5698,7 +5692,7 @@
         <v>FT Bookkeeping - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="109" spans="1:6" hidden="1">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>82</v>
       </c>
@@ -5719,7 +5713,7 @@
         <v>Oracle HCM Cloud Developer - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="110" spans="1:6" hidden="1">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>83</v>
       </c>
@@ -5740,7 +5734,7 @@
         <v>PT Zoho Developer - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="111" spans="1:6" hidden="1">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>84</v>
       </c>
@@ -5761,7 +5755,7 @@
         <v>Full Time Custom Staff Aug - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="112" spans="1:6" hidden="1">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>85</v>
       </c>
@@ -5782,7 +5776,7 @@
         <v>Full Time Medical Staff - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="113" spans="1:6" hidden="1">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>86</v>
       </c>
@@ -5803,7 +5797,7 @@
         <v>Part Time Custom Staff Aug - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="114" spans="1:6" hidden="1">
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>87</v>
       </c>
@@ -5824,7 +5818,7 @@
         <v>PT Accountant - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="115" spans="1:6" hidden="1">
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>88</v>
       </c>
@@ -5845,7 +5839,7 @@
         <v>FT Wealth Management Virtual Assistant - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="116" spans="1:6" hidden="1">
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>89</v>
       </c>
@@ -5866,7 +5860,7 @@
         <v>PT Bookkeeping - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="117" spans="1:6" hidden="1">
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>90</v>
       </c>
@@ -5887,7 +5881,7 @@
         <v>Dedicated 24x7x365 Digital Assistant - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="118" spans="1:6" hidden="1">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>91</v>
       </c>
@@ -5908,7 +5902,7 @@
         <v>Data Analytics Managed Service - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="119" spans="1:6" hidden="1">
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>92</v>
       </c>
@@ -5929,7 +5923,7 @@
         <v>Data Analytics Implementation - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="120" spans="1:6" hidden="1">
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>93</v>
       </c>
@@ -5950,7 +5944,7 @@
         <v>FT RPA Developer - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="121" spans="1:6" hidden="1">
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>94</v>
       </c>
@@ -5971,7 +5965,7 @@
         <v>DA Implementation Team - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="122" spans="1:6" hidden="1">
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>95</v>
       </c>
@@ -5992,7 +5986,7 @@
         <v>AI Data Extraction per page - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="123" spans="1:6" hidden="1">
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>96</v>
       </c>
@@ -6013,7 +6007,7 @@
         <v>Fractional Digital Assistant - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="124" spans="1:6" hidden="1">
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>97</v>
       </c>
@@ -6034,7 +6028,7 @@
         <v>AI Workshop - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="125" spans="1:6" hidden="1">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>98</v>
       </c>
@@ -6055,7 +6049,7 @@
         <v>Background Verification Check Fee - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="126" spans="1:6" hidden="1">
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>99</v>
       </c>
@@ -6076,7 +6070,7 @@
         <v>Onboarding Setup - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="127" spans="1:6" hidden="1">
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>100</v>
       </c>
@@ -6097,7 +6091,7 @@
         <v>T&amp;M Staff Augmentation - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="128" spans="1:6" hidden="1">
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>101</v>
       </c>
@@ -6118,7 +6112,7 @@
         <v>Custom Data Analytics Consulting - T&amp;M - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="129" spans="1:6" hidden="1">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>102</v>
       </c>
@@ -6139,7 +6133,7 @@
         <v>Data Analytics - Basic Maintenance - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="130" spans="1:6" hidden="1">
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>103</v>
       </c>
@@ -6160,7 +6154,7 @@
         <v>Data Analytics - Light Managed Service - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="131" spans="1:6" hidden="1">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>104</v>
       </c>
@@ -6181,7 +6175,7 @@
         <v>Data Analytics - Managed Service - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="132" spans="1:6" hidden="1">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>105</v>
       </c>
@@ -6202,7 +6196,7 @@
         <v>Data Analytics - Prototype Model - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="133" spans="1:6" hidden="1">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>106</v>
       </c>
@@ -6223,7 +6217,7 @@
         <v>Reseller Monthly Fee - GBP - Reseller Pipeline</v>
       </c>
     </row>
-    <row r="134" spans="1:6" hidden="1">
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>107</v>
       </c>
@@ -6244,7 +6238,7 @@
         <v>Franchise Setup Fee  - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="135" spans="1:6" hidden="1">
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
         <v>108</v>
       </c>
@@ -6265,7 +6259,7 @@
         <v>Monthly Lead Gen Tech Stack Fee - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="136" spans="1:6" hidden="1">
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
         <v>109</v>
       </c>
@@ -6307,7 +6301,7 @@
         <v>Monthly Support Fee - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="138" spans="1:6" hidden="1">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>111</v>
       </c>
@@ -6328,7 +6322,7 @@
         <v>Annual Conference Fee - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="139" spans="1:6" hidden="1">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>112</v>
       </c>
@@ -6349,7 +6343,7 @@
         <v>Monthly Consultant Access Fee - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="140" spans="1:6" hidden="1">
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>113</v>
       </c>
@@ -6370,7 +6364,7 @@
         <v>COMPLEX - Ai Powered Data Extraction - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="141" spans="1:6" hidden="1">
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>114</v>
       </c>
@@ -6391,7 +6385,7 @@
         <v>Ai Powered Data Extraction - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="142" spans="1:6" hidden="1">
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>115</v>
       </c>
@@ -6412,7 +6406,7 @@
         <v>Digital Assistant - upto 250k Executions - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="143" spans="1:6" hidden="1">
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>116</v>
       </c>
@@ -6433,7 +6427,7 @@
         <v>Digital Assistant - upto 100k Executions - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="144" spans="1:6" hidden="1">
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
         <v>117</v>
       </c>
@@ -6454,7 +6448,7 @@
         <v>Digital Assistant - upto 50k Executions - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="145" spans="1:6" hidden="1">
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>118</v>
       </c>
@@ -6475,7 +6469,7 @@
         <v>Digital Assistant - upto 10k Executions - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="146" spans="1:6" hidden="1">
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>119</v>
       </c>
@@ -6496,7 +6490,7 @@
         <v>MSP Reseller - GBP - MSP Pipeline</v>
       </c>
     </row>
-    <row r="147" spans="1:6" hidden="1">
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
         <v>121</v>
       </c>
@@ -6517,7 +6511,7 @@
         <v>MSP Referral Partner - GBP - MSP Pipeline</v>
       </c>
     </row>
-    <row r="148" spans="1:6" hidden="1">
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
         <v>122</v>
       </c>
@@ -6538,7 +6532,7 @@
         <v>MSP Service Delivery Partner - GBP - MSP Pipeline</v>
       </c>
     </row>
-    <row r="149" spans="1:6" hidden="1">
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
         <v>126</v>
       </c>
@@ -6559,7 +6553,7 @@
         <v>Consultant - Dripify License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="150" spans="1:6" hidden="1">
+    <row r="150" spans="1:6">
       <c r="A150" t="s">
         <v>127</v>
       </c>
@@ -6580,7 +6574,7 @@
         <v>1Password License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="151" spans="1:6" hidden="1">
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
         <v>128</v>
       </c>
@@ -6601,7 +6595,7 @@
         <v>Consultant - MS Email Only + 1Password - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="152" spans="1:6" hidden="1">
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
         <v>129</v>
       </c>
@@ -6622,7 +6616,7 @@
         <v>Consultant - HubSpot Sales License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="153" spans="1:6" hidden="1">
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
         <v>130</v>
       </c>
@@ -6643,7 +6637,7 @@
         <v>Consultant - MS CoPilot License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="154" spans="1:6" hidden="1">
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
         <v>131</v>
       </c>
@@ -6664,7 +6658,7 @@
         <v>HubSpot Sales License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="155" spans="1:6" hidden="1">
+    <row r="155" spans="1:6">
       <c r="A155" t="s">
         <v>132</v>
       </c>
@@ -6685,7 +6679,7 @@
         <v>Consultant - Apollo License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="156" spans="1:6" hidden="1">
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
         <v>133</v>
       </c>
@@ -6706,7 +6700,7 @@
         <v>Consultant - MS Email Only - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="157" spans="1:6" hidden="1">
+    <row r="157" spans="1:6">
       <c r="A157" t="s">
         <v>134</v>
       </c>
@@ -6727,7 +6721,7 @@
         <v>Consultant - MS O365 License + 1Password - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="158" spans="1:6" hidden="1">
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
         <v>135</v>
       </c>
@@ -6748,7 +6742,7 @@
         <v>Dripify License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="159" spans="1:6" hidden="1">
+    <row r="159" spans="1:6">
       <c r="A159" t="s">
         <v>136</v>
       </c>
@@ -6769,7 +6763,7 @@
         <v>Monthly Annual Conference Fee - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="160" spans="1:6" hidden="1">
+    <row r="160" spans="1:6">
       <c r="A160" t="s">
         <v>137</v>
       </c>
@@ -6790,7 +6784,7 @@
         <v>MS CoPilot License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="161" spans="1:6" hidden="1">
+    <row r="161" spans="1:6">
       <c r="A161" t="s">
         <v>138</v>
       </c>
@@ -6811,7 +6805,7 @@
         <v>MS O365 License + 1Password - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="162" spans="1:6" hidden="1">
+    <row r="162" spans="1:6">
       <c r="A162" t="s">
         <v>139</v>
       </c>
@@ -6832,7 +6826,7 @@
         <v>Apollo License - AUD - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="163" spans="1:6" hidden="1">
+    <row r="163" spans="1:6">
       <c r="A163" t="s">
         <v>140</v>
       </c>
@@ -6853,7 +6847,7 @@
         <v>Data Analyst - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="164" spans="1:6" hidden="1">
+    <row r="164" spans="1:6">
       <c r="A164" t="s">
         <v>141</v>
       </c>
@@ -6874,7 +6868,7 @@
         <v>Reseller International - AUD - Reseller Pipeline</v>
       </c>
     </row>
-    <row r="165" spans="1:6" hidden="1">
+    <row r="165" spans="1:6">
       <c r="A165" t="s">
         <v>106</v>
       </c>
@@ -6895,7 +6889,7 @@
         <v>Reseller Monthly Fee - AUD - Reseller Pipeline</v>
       </c>
     </row>
-    <row r="166" spans="1:6" hidden="1">
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
         <v>126</v>
       </c>
@@ -6916,7 +6910,7 @@
         <v>Consultant - Dripify License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="167" spans="1:6" hidden="1">
+    <row r="167" spans="1:6">
       <c r="A167" t="s">
         <v>127</v>
       </c>
@@ -6937,7 +6931,7 @@
         <v>1Password License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="168" spans="1:6" hidden="1">
+    <row r="168" spans="1:6">
       <c r="A168" t="s">
         <v>128</v>
       </c>
@@ -6958,7 +6952,7 @@
         <v>Consultant - MS Email Only + 1Password - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="169" spans="1:6" hidden="1">
+    <row r="169" spans="1:6">
       <c r="A169" t="s">
         <v>129</v>
       </c>
@@ -6979,7 +6973,7 @@
         <v>Consultant - HubSpot Sales License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="170" spans="1:6" hidden="1">
+    <row r="170" spans="1:6">
       <c r="A170" t="s">
         <v>130</v>
       </c>
@@ -7000,7 +6994,7 @@
         <v>Consultant - MS CoPilot License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="171" spans="1:6" hidden="1">
+    <row r="171" spans="1:6">
       <c r="A171" t="s">
         <v>131</v>
       </c>
@@ -7021,7 +7015,7 @@
         <v>HubSpot Sales License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="172" spans="1:6" hidden="1">
+    <row r="172" spans="1:6">
       <c r="A172" t="s">
         <v>132</v>
       </c>
@@ -7042,7 +7036,7 @@
         <v>Consultant - Apollo License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="173" spans="1:6" hidden="1">
+    <row r="173" spans="1:6">
       <c r="A173" t="s">
         <v>133</v>
       </c>
@@ -7063,7 +7057,7 @@
         <v>Consultant - MS Email Only - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="174" spans="1:6" hidden="1">
+    <row r="174" spans="1:6">
       <c r="A174" t="s">
         <v>134</v>
       </c>
@@ -7084,7 +7078,7 @@
         <v>Consultant - MS O365 License + 1Password - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="175" spans="1:6" hidden="1">
+    <row r="175" spans="1:6">
       <c r="A175" t="s">
         <v>135</v>
       </c>
@@ -7105,7 +7099,7 @@
         <v>Dripify License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="176" spans="1:6" hidden="1">
+    <row r="176" spans="1:6">
       <c r="A176" t="s">
         <v>136</v>
       </c>
@@ -7126,7 +7120,7 @@
         <v>Monthly Annual Conference Fee - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="177" spans="1:6" hidden="1">
+    <row r="177" spans="1:6">
       <c r="A177" t="s">
         <v>137</v>
       </c>
@@ -7147,7 +7141,7 @@
         <v>MS CoPilot License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="178" spans="1:6" hidden="1">
+    <row r="178" spans="1:6">
       <c r="A178" t="s">
         <v>138</v>
       </c>
@@ -7168,7 +7162,7 @@
         <v>MS O365 License + 1Password - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="179" spans="1:6" hidden="1">
+    <row r="179" spans="1:6">
       <c r="A179" t="s">
         <v>139</v>
       </c>
@@ -7189,7 +7183,7 @@
         <v>Apollo License - GBP - Franchise Pipeline</v>
       </c>
     </row>
-    <row r="180" spans="1:6" hidden="1">
+    <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>140</v>
       </c>
@@ -7210,7 +7204,7 @@
         <v>Data Analyst - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="181" spans="1:6" hidden="1">
+    <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>141</v>
       </c>
@@ -7231,7 +7225,7 @@
         <v>Reseller International - GBP - Reseller Pipeline</v>
       </c>
     </row>
-    <row r="182" spans="1:6" hidden="1">
+    <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>142</v>
       </c>
@@ -7252,7 +7246,7 @@
         <v>Client Staff Bonus - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="183" spans="1:6" hidden="1">
+    <row r="183" spans="1:6">
       <c r="A183" t="s">
         <v>142</v>
       </c>
@@ -7273,7 +7267,7 @@
         <v>Client Staff Bonus - GBP - Sales Pipeline</v>
       </c>
     </row>
-    <row r="184" spans="1:6" hidden="1">
+    <row r="184" spans="1:6">
       <c r="A184" t="s">
         <v>145</v>
       </c>
@@ -7294,7 +7288,7 @@
         <v>Staff Aug 1.5x Project - AUD - Sales Pipeline</v>
       </c>
     </row>
-    <row r="185" spans="1:6" hidden="1">
+    <row r="185" spans="1:6">
       <c r="A185" t="s">
         <v>145</v>
       </c>
@@ -7324,6 +7318,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="2b4b3f37-1cd0-4b26-90f2-9948314503a5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca9c0abd-4151-432c-97d3-4a3f10bfee7f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005F54BCC7603DAA4FB57C31851CA92685" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b666b694d6e76699e884a198b0fcc20b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ca9c0abd-4151-432c-97d3-4a3f10bfee7f" xmlns:ns3="2b4b3f37-1cd0-4b26-90f2-9948314503a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3e06c0a76cf39f93bdfa440a1b88f7bb" ns2:_="" ns3:_="">
     <xsd:import namespace="ca9c0abd-4151-432c-97d3-4a3f10bfee7f"/>
@@ -7564,28 +7578,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="2b4b3f37-1cd0-4b26-90f2-9948314503a5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca9c0abd-4151-432c-97d3-4a3f10bfee7f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0554FEC5-F8C0-4A0B-9C72-9FC3334369E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60A3338-C622-4FF5-BFA9-54DFDA479994}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7593,5 +7587,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60A3338-C622-4FF5-BFA9-54DFDA479994}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0554FEC5-F8C0-4A0B-9C72-9FC3334369E2}"/>
 </file>
--- a/Data/Temp/InvoicesReport UI Extraction.xlsx
+++ b/Data/Temp/InvoicesReport UI Extraction.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanielRicardoRochaQu\Downloads\Invoicing Bot\Recon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1221" documentId="13_ncr:1_{B5D6CEAF-E681-4588-8E6E-EF4492DB7BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1E9BAF7-DFE4-4C3B-83CC-F19F6A125004}"/>
+  <xr:revisionPtr revIDLastSave="1226" documentId="13_ncr:1_{B5D6CEAF-E681-4588-8E6E-EF4492DB7BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66D66237-DC5E-4EE5-B06E-1ADCCD14582E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="6" xr2:uid="{70E8A791-13CE-4BD4-B2C5-703777F4F9B6}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="146">
   <si>
     <t>RECORD ID - INVOICES</t>
   </si>
@@ -1055,7 +1055,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1067,6 +1067,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1406,8 +1407,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}" name="Xero_Tax_Acc" displayName="Xero_Tax_Acc" ref="A1:F185" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:F185" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}" name="Xero_Tax_Acc" displayName="Xero_Tax_Acc" ref="A1:F186" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:F186" xr:uid="{665A5D82-60EC-45BF-9AFF-3D1DD22F2701}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{ADF06759-72AB-4C84-B20B-0E8D66CF7A70}" name="Line Item"/>
     <tableColumn id="4" xr3:uid="{136FB1F1-5689-4097-ACD2-3191F8E3FAEA}" name="Currency"/>
@@ -3414,7 +3415,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06CC148B-0B9B-443B-9640-E0693778E85E}">
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
@@ -7309,6 +7310,27 @@
         <v>Staff Aug 1.5x Project - GBP - Sales Pipeline</v>
       </c>
     </row>
+    <row r="186" spans="1:6">
+      <c r="A186" t="s">
+        <v>142</v>
+      </c>
+      <c r="B186" t="s">
+        <v>47</v>
+      </c>
+      <c r="C186" t="s">
+        <v>41</v>
+      </c>
+      <c r="D186" t="s">
+        <v>123</v>
+      </c>
+      <c r="E186">
+        <v>280</v>
+      </c>
+      <c r="F186" s="11" t="str">
+        <f>+CONCATENATE(Xero_Tax_Acc[[#This Row],[Line Item]]," - ",Xero_Tax_Acc[[#This Row],[Currency]]," - ",Xero_Tax_Acc[[#This Row],[Pipeline]])</f>
+        <v>Client Staff Bonus - NZD - Sales Pipeline</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -7318,26 +7340,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="2b4b3f37-1cd0-4b26-90f2-9948314503a5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca9c0abd-4151-432c-97d3-4a3f10bfee7f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005F54BCC7603DAA4FB57C31851CA92685" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b666b694d6e76699e884a198b0fcc20b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ca9c0abd-4151-432c-97d3-4a3f10bfee7f" xmlns:ns3="2b4b3f37-1cd0-4b26-90f2-9948314503a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3e06c0a76cf39f93bdfa440a1b88f7bb" ns2:_="" ns3:_="">
     <xsd:import namespace="ca9c0abd-4151-432c-97d3-4a3f10bfee7f"/>
@@ -7578,8 +7580,28 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="2b4b3f37-1cd0-4b26-90f2-9948314503a5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ca9c0abd-4151-432c-97d3-4a3f10bfee7f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60A3338-C622-4FF5-BFA9-54DFDA479994}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0554FEC5-F8C0-4A0B-9C72-9FC3334369E2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7587,5 +7609,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0554FEC5-F8C0-4A0B-9C72-9FC3334369E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60A3338-C622-4FF5-BFA9-54DFDA479994}"/>
 </file>